--- a/files/SP_MasterFile.xlsx
+++ b/files/SP_MasterFile.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29912"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10302"/>
   <workbookPr filterPrivacy="1" showInkAnnotation="0" codeName="ThisWorkbook"/>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{4AC0A365-BB9A-4F9B-9445-33CAC8F20F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="630" yWindow="-120" windowWidth="28290" windowHeight="16440" tabRatio="832" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-47040" yWindow="-4980" windowWidth="28300" windowHeight="16440" tabRatio="832" firstSheet="8" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Autocall" sheetId="1" r:id="rId1"/>
@@ -4195,7 +4195,7 @@
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="36" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8814,22 +8814,22 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:N52"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="17.1640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.33203125" style="1" customWidth="1"/>
     <col min="3" max="5" width="36.5" style="1" customWidth="1"/>
-    <col min="6" max="6" width="42.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="42.1640625" style="1" customWidth="1"/>
     <col min="7" max="7" width="39.5" style="1" customWidth="1"/>
     <col min="8" max="8" width="35" style="1" customWidth="1"/>
     <col min="9" max="9" width="32.5" style="1" customWidth="1"/>
-    <col min="10" max="10" width="42.125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="40.625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="42.1640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="40.6640625" style="1" customWidth="1"/>
     <col min="12" max="14" width="36.5" style="1" customWidth="1"/>
     <col min="15" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.2">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8870,7 +8870,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A2" s="8"/>
       <c r="B2" s="117" t="s">
         <v>12</v>
@@ -8912,7 +8912,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:14" ht="15.75">
+    <row r="3" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A3" s="9"/>
       <c r="B3" s="174" t="s">
         <v>23</v>
@@ -8954,7 +8954,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
         <v>36</v>
       </c>
@@ -8998,7 +8998,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>38</v>
       </c>
@@ -9042,7 +9042,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>42</v>
       </c>
@@ -9086,7 +9086,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>48</v>
       </c>
@@ -9112,7 +9112,7 @@
       <c r="M7" s="175"/>
       <c r="N7" s="11"/>
     </row>
-    <row r="8" spans="1:14" ht="135.75" thickBot="1">
+    <row r="8" spans="1:14" ht="129" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="20" t="s">
         <v>50</v>
       </c>
@@ -9156,7 +9156,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="9" spans="1:14" ht="15.75" thickBot="1">
+    <row r="9" spans="1:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="100" t="s">
         <v>63</v>
       </c>
@@ -9200,7 +9200,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A10" s="260" t="s">
         <v>64</v>
       </c>
@@ -9218,7 +9218,7 @@
       <c r="M10" s="236"/>
       <c r="N10" s="236"/>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A11" s="260" t="s">
         <v>65</v>
       </c>
@@ -9236,7 +9236,7 @@
       <c r="M11" s="236"/>
       <c r="N11" s="236"/>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A12" s="260" t="s">
         <v>66</v>
       </c>
@@ -9280,7 +9280,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A13" s="260" t="s">
         <v>66</v>
       </c>
@@ -9324,7 +9324,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A14" s="260" t="s">
         <v>66</v>
       </c>
@@ -9368,7 +9368,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" ht="16" x14ac:dyDescent="0.2">
       <c r="A15" s="260" t="s">
         <v>66</v>
       </c>
@@ -9390,7 +9390,7 @@
       <c r="M15" s="236"/>
       <c r="N15" s="236"/>
     </row>
-    <row r="16" spans="1:14" s="263" customFormat="1" ht="15" customHeight="1">
+    <row r="16" spans="1:14" s="263" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="262" t="s">
         <v>79</v>
       </c>
@@ -9434,7 +9434,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A17" s="93"/>
       <c r="B17" s="236"/>
       <c r="C17" s="236"/>
@@ -9450,7 +9450,7 @@
       <c r="M17" s="236"/>
       <c r="N17" s="236"/>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A18" s="93"/>
       <c r="B18" s="236"/>
       <c r="C18" s="236"/>
@@ -9466,7 +9466,7 @@
       <c r="M18" s="236"/>
       <c r="N18" s="236"/>
     </row>
-    <row r="19" spans="1:14" s="7" customFormat="1" ht="30.75" thickBot="1">
+    <row r="19" spans="1:14" s="7" customFormat="1" ht="33" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A19" s="94" t="s">
         <v>81</v>
       </c>
@@ -9510,7 +9510,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="20" spans="1:14" s="4" customFormat="1">
+    <row r="20" spans="1:14" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="40"/>
       <c r="B20" s="41" t="s">
         <v>83</v>
@@ -9552,7 +9552,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="21" spans="1:14" s="4" customFormat="1" ht="60">
+    <row r="21" spans="1:14" s="4" customFormat="1" ht="64" x14ac:dyDescent="0.2">
       <c r="A21" s="5" t="s">
         <v>84</v>
       </c>
@@ -9596,7 +9596,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="22" spans="1:14" s="2" customFormat="1" ht="66.75" customHeight="1">
+    <row r="22" spans="1:14" s="2" customFormat="1" ht="66.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B22" s="60" t="s">
         <v>88</v>
       </c>
@@ -9637,7 +9637,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="23" spans="1:14" s="2" customFormat="1" ht="129" customHeight="1">
+    <row r="23" spans="1:14" s="2" customFormat="1" ht="129" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A23" s="6"/>
       <c r="B23" s="60" t="s">
         <v>90</v>
@@ -9679,7 +9679,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="24" spans="1:14" s="2" customFormat="1" ht="120">
+    <row r="24" spans="1:14" s="2" customFormat="1" ht="128" x14ac:dyDescent="0.15">
       <c r="A24" s="6"/>
       <c r="B24" s="60" t="s">
         <v>100</v>
@@ -9721,7 +9721,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="25" spans="1:14" s="2" customFormat="1" ht="285">
+    <row r="25" spans="1:14" s="2" customFormat="1" ht="288" x14ac:dyDescent="0.15">
       <c r="A25" s="6"/>
       <c r="B25" s="60" t="s">
         <v>112</v>
@@ -9763,7 +9763,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="26" spans="1:14" s="2" customFormat="1" ht="360">
+    <row r="26" spans="1:14" s="2" customFormat="1" ht="365" x14ac:dyDescent="0.15">
       <c r="A26" s="6"/>
       <c r="B26" s="60" t="s">
         <v>124</v>
@@ -9791,7 +9791,7 @@
       </c>
       <c r="N26" s="30"/>
     </row>
-    <row r="27" spans="1:14" s="2" customFormat="1">
+    <row r="27" spans="1:14" s="2" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A27" s="47"/>
       <c r="B27" s="30"/>
       <c r="C27" s="30"/>
@@ -9804,7 +9804,7 @@
       <c r="L27" s="30"/>
       <c r="M27" s="30"/>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A28" s="13" t="s">
         <v>130</v>
       </c>
@@ -9822,7 +9822,7 @@
       <c r="M28" s="80"/>
       <c r="N28" s="80"/>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A29" s="13"/>
       <c r="B29" s="104" t="s">
         <v>131</v>
@@ -9864,7 +9864,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="30" spans="1:14" s="16" customFormat="1">
+    <row r="30" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A30" s="15"/>
       <c r="B30" s="104" t="s">
         <v>132</v>
@@ -9906,7 +9906,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="31" spans="1:14" s="16" customFormat="1">
+    <row r="31" spans="1:14" s="16" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A31" s="15"/>
       <c r="B31" s="104" t="s">
         <v>133</v>
@@ -9948,7 +9948,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="32" spans="1:14" s="12" customFormat="1">
+    <row r="32" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A32" s="13"/>
       <c r="B32" s="12" t="s">
         <v>134</v>
@@ -9990,7 +9990,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="33" spans="1:14" s="12" customFormat="1">
+    <row r="33" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A33" s="13"/>
       <c r="B33" s="12" t="s">
         <v>135</v>
@@ -10032,7 +10032,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="34" spans="1:14" s="12" customFormat="1">
+    <row r="34" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A34" s="13"/>
       <c r="B34" s="12" t="s">
         <v>137</v>
@@ -10074,7 +10074,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="35" spans="1:14" s="12" customFormat="1">
+    <row r="35" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A35" s="13"/>
       <c r="B35" s="12" t="s">
         <v>141</v>
@@ -10116,7 +10116,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="36" spans="1:14" s="12" customFormat="1">
+    <row r="36" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A36" s="13"/>
       <c r="B36" s="12" t="s">
         <v>142</v>
@@ -10158,7 +10158,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="37" spans="1:14" s="12" customFormat="1">
+    <row r="37" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A37" s="13"/>
       <c r="B37" s="12" t="s">
         <v>143</v>
@@ -10200,7 +10200,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="38" spans="1:14" s="12" customFormat="1">
+    <row r="38" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A38" s="13"/>
       <c r="B38" s="12" t="s">
         <v>144</v>
@@ -10242,7 +10242,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="39" spans="1:14" s="12" customFormat="1">
+    <row r="39" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A39" s="13"/>
       <c r="B39" s="12" t="s">
         <v>146</v>
@@ -10284,7 +10284,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="40" spans="1:14">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A40" s="13"/>
       <c r="B40" s="12" t="s">
         <v>145</v>
@@ -10322,7 +10322,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="41" spans="1:14">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.2">
       <c r="A41" s="13"/>
       <c r="B41" s="12" t="s">
         <v>148</v>
@@ -10352,7 +10352,7 @@
       </c>
       <c r="N41" s="12"/>
     </row>
-    <row r="42" spans="1:14" s="12" customFormat="1">
+    <row r="42" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B42" s="12" t="s">
         <v>147</v>
       </c>
@@ -10375,7 +10375,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="43" spans="1:14" s="12" customFormat="1">
+    <row r="43" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A43" s="13"/>
       <c r="D43" s="183" t="s">
         <v>149</v>
@@ -10396,7 +10396,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="44" spans="1:14" s="12" customFormat="1">
+    <row r="44" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A44" s="13"/>
       <c r="C44" s="183" t="s">
         <v>149</v>
@@ -10411,29 +10411,29 @@
         <v>149</v>
       </c>
     </row>
-    <row r="45" spans="1:14" s="12" customFormat="1">
+    <row r="45" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A45" s="13"/>
       <c r="B45" s="183" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="46" spans="1:14" s="12" customFormat="1">
+    <row r="46" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A46" s="13"/>
       <c r="C46" s="1"/>
       <c r="M46" s="1"/>
     </row>
-    <row r="47" spans="1:14" s="12" customFormat="1">
+    <row r="47" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A47" s="13"/>
       <c r="C47" s="1"/>
       <c r="M47" s="1"/>
     </row>
-    <row r="48" spans="1:14" s="12" customFormat="1">
+    <row r="48" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A48" s="13"/>
       <c r="B48" s="1"/>
       <c r="C48" s="1"/>
       <c r="M48" s="1"/>
     </row>
-    <row r="49" spans="1:14" s="12" customFormat="1">
+    <row r="49" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A49" s="13"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
@@ -10441,7 +10441,7 @@
       <c r="M49" s="1"/>
       <c r="N49" s="1"/>
     </row>
-    <row r="50" spans="1:14" s="12" customFormat="1">
+    <row r="50" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A50" s="13"/>
       <c r="B50" s="1"/>
       <c r="C50" s="1"/>
@@ -10451,7 +10451,7 @@
       <c r="M50" s="1"/>
       <c r="N50" s="1"/>
     </row>
-    <row r="51" spans="1:14" s="12" customFormat="1">
+    <row r="51" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A51" s="13"/>
       <c r="B51" s="1"/>
       <c r="C51" s="1"/>
@@ -10466,7 +10466,7 @@
       <c r="M51" s="1"/>
       <c r="N51" s="1"/>
     </row>
-    <row r="52" spans="1:14" s="12" customFormat="1">
+    <row r="52" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A52" s="13"/>
       <c r="B52" s="1"/>
       <c r="C52" s="1"/>
@@ -10495,14 +10495,14 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:K37"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="9" width="37.375" style="1" customWidth="1"/>
-    <col min="10" max="11" width="32.25" customWidth="1"/>
+    <col min="1" max="1" width="17.1640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="9" width="37.33203125" style="1" customWidth="1"/>
+    <col min="10" max="11" width="32.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A1" s="61"/>
       <c r="B1" s="117"/>
       <c r="C1" s="117"/>
@@ -10513,7 +10513,7 @@
       <c r="H1" s="117"/>
       <c r="I1" s="117"/>
     </row>
-    <row r="2" spans="1:11" ht="15.75">
+    <row r="2" spans="1:11" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="9"/>
       <c r="B2" s="174" t="s">
         <v>1140</v>
@@ -10540,7 +10540,7 @@
         <v>1147</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
         <v>36</v>
       </c>
@@ -10569,7 +10569,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
         <v>38</v>
       </c>
@@ -10598,7 +10598,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>42</v>
       </c>
@@ -10627,7 +10627,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>48</v>
       </c>
@@ -10656,7 +10656,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>534</v>
       </c>
@@ -10685,7 +10685,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="15.75" thickBot="1">
+    <row r="8" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>824</v>
       </c>
@@ -10714,7 +10714,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="150.75" thickBot="1">
+    <row r="9" spans="1:11" ht="161" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A9" s="20" t="s">
         <v>50</v>
       </c>
@@ -10743,7 +10743,7 @@
         <v>1162</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="15.75" thickBot="1">
+    <row r="10" spans="1:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="103" t="s">
         <v>63</v>
       </c>
@@ -10772,7 +10772,7 @@
         <v>1300</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A11" s="136" t="s">
         <v>81</v>
       </c>
@@ -10801,7 +10801,7 @@
         <v>555</v>
       </c>
     </row>
-    <row r="12" spans="1:11" s="7" customFormat="1">
+    <row r="12" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="138"/>
       <c r="B12" s="134" t="s">
         <v>1163</v>
@@ -10828,7 +10828,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A13" s="14"/>
       <c r="B13" s="116" t="s">
         <v>83</v>
@@ -10855,7 +10855,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="14" spans="1:11" s="49" customFormat="1" ht="45">
+    <row r="14" spans="1:11" s="49" customFormat="1" ht="48" x14ac:dyDescent="0.15">
       <c r="A14" s="5" t="s">
         <v>84</v>
       </c>
@@ -10884,7 +10884,7 @@
         <v>1168</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="80.25" customHeight="1">
+    <row r="15" spans="1:11" ht="80.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15"/>
       <c r="B15" s="60" t="s">
         <v>1169</v>
@@ -10911,7 +10911,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="16" spans="1:11" ht="195">
+    <row r="16" spans="1:11" ht="208" x14ac:dyDescent="0.15">
       <c r="A16" s="6"/>
       <c r="B16" s="30" t="s">
         <v>1170</v>
@@ -10940,7 +10940,7 @@
       <c r="J16" s="60"/>
       <c r="K16" s="60"/>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A17" s="6"/>
       <c r="B17" s="60"/>
       <c r="C17" s="60"/>
@@ -10951,7 +10951,7 @@
       <c r="H17" s="60"/>
       <c r="I17" s="60"/>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A18" s="47"/>
       <c r="B18" s="30"/>
       <c r="C18" s="60"/>
@@ -10962,7 +10962,7 @@
       <c r="H18" s="60"/>
       <c r="I18" s="60"/>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.15">
       <c r="A19" s="47"/>
       <c r="B19" s="60"/>
       <c r="C19" s="2"/>
@@ -10973,13 +10973,13 @@
       <c r="H19" s="2"/>
       <c r="I19" s="2"/>
     </row>
-    <row r="20" spans="1:9">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="13" t="s">
         <v>406</v>
       </c>
       <c r="B20" s="60"/>
     </row>
-    <row r="21" spans="1:9">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="15"/>
       <c r="B21" s="69" t="s">
         <v>1178</v>
@@ -11006,7 +11006,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="13"/>
       <c r="B22" s="12" t="s">
         <v>1179</v>
@@ -11033,7 +11033,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="13"/>
       <c r="B23" s="12" t="s">
         <v>1180</v>
@@ -11060,7 +11060,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="13"/>
       <c r="B24" s="12" t="s">
         <v>134</v>
@@ -11087,7 +11087,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="13"/>
       <c r="C25" s="12" t="s">
         <v>134</v>
@@ -11105,7 +11105,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="12"/>
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
@@ -11116,7 +11116,7 @@
       <c r="H26" s="12"/>
       <c r="I26" s="12"/>
     </row>
-    <row r="27" spans="1:9">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="13"/>
       <c r="B27" s="69"/>
       <c r="C27" s="12"/>
@@ -11127,7 +11127,7 @@
       <c r="H27" s="12"/>
       <c r="I27" s="12"/>
     </row>
-    <row r="28" spans="1:9">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="13"/>
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
@@ -11138,7 +11138,7 @@
       <c r="H28" s="12"/>
       <c r="I28" s="12"/>
     </row>
-    <row r="29" spans="1:9">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="13"/>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
@@ -11149,37 +11149,37 @@
       <c r="H29" s="12"/>
       <c r="I29" s="12"/>
     </row>
-    <row r="30" spans="1:9">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="13"/>
       <c r="B30" s="12"/>
       <c r="E30" s="12"/>
       <c r="G30" s="12"/>
       <c r="I30" s="12"/>
     </row>
-    <row r="31" spans="1:9">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="13"/>
     </row>
-    <row r="32" spans="1:9">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="13"/>
     </row>
-    <row r="33" spans="1:9">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="13"/>
     </row>
-    <row r="34" spans="1:9">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="13"/>
       <c r="B34" s="12"/>
     </row>
-    <row r="35" spans="1:9">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="13"/>
     </row>
-    <row r="36" spans="1:9">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="13"/>
       <c r="C36" s="12"/>
       <c r="D36" s="12"/>
       <c r="F36" s="12"/>
       <c r="H36" s="12"/>
     </row>
-    <row r="37" spans="1:9">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="13"/>
       <c r="E37" s="12"/>
       <c r="G37" s="12"/>
@@ -11198,20 +11198,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I39"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="37.375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="17.1640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="37.33203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="61"/>
       <c r="B1" s="117"/>
       <c r="C1" s="117"/>
       <c r="D1" s="117"/>
       <c r="E1" s="117"/>
     </row>
-    <row r="2" spans="1:9" ht="15.75">
+    <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="9"/>
       <c r="B2" s="174" t="s">
         <v>1181</v>
@@ -11226,7 +11226,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
         <v>36</v>
       </c>
@@ -11243,7 +11243,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
         <v>38</v>
       </c>
@@ -11260,7 +11260,7 @@
         <v>1186</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>42</v>
       </c>
@@ -11277,7 +11277,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>48</v>
       </c>
@@ -11294,7 +11294,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>534</v>
       </c>
@@ -11311,7 +11311,7 @@
         <v>1190</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.75" thickBot="1">
+    <row r="8" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>824</v>
       </c>
@@ -11328,7 +11328,7 @@
         <v>1191</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="135.75" thickBot="1">
+    <row r="9" spans="1:9" ht="145" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A9" s="20" t="s">
         <v>50</v>
       </c>
@@ -11345,7 +11345,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="15.75" thickBot="1">
+    <row r="10" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="103" t="s">
         <v>63</v>
       </c>
@@ -11362,7 +11362,7 @@
         <v>2100</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="136" t="s">
         <v>81</v>
       </c>
@@ -11383,7 +11383,7 @@
       <c r="H11" s="129"/>
       <c r="I11" s="129"/>
     </row>
-    <row r="12" spans="1:9" s="7" customFormat="1">
+    <row r="12" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="102"/>
       <c r="B12" s="134" t="s">
         <v>557</v>
@@ -11398,7 +11398,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="14"/>
       <c r="B13" s="116" t="s">
         <v>83</v>
@@ -11413,7 +11413,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="60">
+    <row r="14" spans="1:9" ht="64" x14ac:dyDescent="0.2">
       <c r="A14" s="5" t="s">
         <v>84</v>
       </c>
@@ -11430,7 +11430,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="53.25" customHeight="1">
+    <row r="15" spans="1:9" ht="53.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A15"/>
       <c r="B15" s="60" t="s">
         <v>1198</v>
@@ -11445,7 +11445,7 @@
         <v>1198</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="126.75" customHeight="1">
+    <row r="16" spans="1:9" ht="126.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="6"/>
       <c r="B16" s="60" t="s">
         <v>1199</v>
@@ -11460,7 +11460,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="54.75" customHeight="1">
+    <row r="17" spans="1:5" ht="54.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="47"/>
       <c r="B17" s="60" t="s">
         <v>1201</v>
@@ -11475,7 +11475,7 @@
         <v>1202</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="45">
+    <row r="18" spans="1:5" ht="48" x14ac:dyDescent="0.15">
       <c r="A18" s="47"/>
       <c r="B18" s="60" t="s">
         <v>1203</v>
@@ -11486,28 +11486,28 @@
       </c>
       <c r="E18" s="60"/>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A19" s="47"/>
       <c r="B19" s="30"/>
       <c r="C19" s="60"/>
       <c r="D19" s="60"/>
       <c r="E19" s="60"/>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A20" s="47"/>
       <c r="B20" s="60"/>
       <c r="C20" s="60"/>
       <c r="D20" s="2"/>
       <c r="E20" s="60"/>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A21" s="47"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="13" t="s">
         <v>406</v>
       </c>
@@ -11524,7 +11524,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="15"/>
       <c r="B23" s="12" t="s">
         <v>1179</v>
@@ -11539,7 +11539,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="13"/>
       <c r="B24" s="12" t="s">
         <v>1204</v>
@@ -11554,7 +11554,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="13"/>
       <c r="B25" s="12" t="s">
         <v>1205</v>
@@ -11569,7 +11569,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="13"/>
       <c r="B26" s="12" t="s">
         <v>134</v>
@@ -11584,7 +11584,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="13"/>
       <c r="B27" s="12" t="s">
         <v>146</v>
@@ -11599,7 +11599,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="12"/>
       <c r="B28" s="12" t="s">
         <v>147</v>
@@ -11614,50 +11614,50 @@
         <v>147</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="13"/>
       <c r="B29" s="12"/>
       <c r="C29" s="12"/>
       <c r="D29" s="12"/>
       <c r="E29" s="12"/>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="13"/>
       <c r="B30" s="12"/>
       <c r="C30" s="12"/>
       <c r="D30" s="12"/>
       <c r="E30" s="12"/>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="13"/>
       <c r="C31" s="12"/>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="13"/>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="13"/>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="13"/>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="13"/>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="13"/>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="13"/>
       <c r="B37" s="12"/>
       <c r="D37" s="12"/>
       <c r="E37" s="12"/>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="13"/>
       <c r="C38" s="12"/>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A39" s="13"/>
     </row>
   </sheetData>
@@ -11673,20 +11673,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I38"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="37.375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="17.1640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="37.33203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="61"/>
       <c r="B1" s="117"/>
       <c r="C1" s="117"/>
       <c r="D1" s="117"/>
       <c r="E1" s="117"/>
     </row>
-    <row r="2" spans="1:9" ht="15.75">
+    <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="9"/>
       <c r="B2" s="174" t="s">
         <v>1206</v>
@@ -11701,7 +11701,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
         <v>36</v>
       </c>
@@ -11718,7 +11718,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
         <v>38</v>
       </c>
@@ -11735,7 +11735,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>42</v>
       </c>
@@ -11752,7 +11752,7 @@
         <v>1151</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>48</v>
       </c>
@@ -11769,7 +11769,7 @@
         <v>1152</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>534</v>
       </c>
@@ -11786,7 +11786,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="10"/>
       <c r="B8" s="175" t="s">
         <v>1213</v>
@@ -11801,7 +11801,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="15.75" thickBot="1">
+    <row r="9" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A9" s="10" t="s">
         <v>824</v>
       </c>
@@ -11818,7 +11818,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="210.75" thickBot="1">
+    <row r="10" spans="1:9" ht="209" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A10" s="20" t="s">
         <v>50</v>
       </c>
@@ -11835,7 +11835,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="15.75" thickBot="1">
+    <row r="11" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="103" t="s">
         <v>63</v>
       </c>
@@ -11852,7 +11852,7 @@
         <v>2210</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="136" t="s">
         <v>81</v>
       </c>
@@ -11873,7 +11873,7 @@
       <c r="H12" s="129"/>
       <c r="I12" s="129"/>
     </row>
-    <row r="13" spans="1:9" s="7" customFormat="1">
+    <row r="13" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="102"/>
       <c r="B13" s="134" t="s">
         <v>1218</v>
@@ -11888,7 +11888,7 @@
         <v>1218</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="14"/>
       <c r="B14" s="116" t="s">
         <v>83</v>
@@ -11903,7 +11903,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="60">
+    <row r="15" spans="1:9" ht="64" x14ac:dyDescent="0.2">
       <c r="A15" s="5" t="s">
         <v>84</v>
       </c>
@@ -11920,7 +11920,7 @@
         <v>1220</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="75">
+    <row r="16" spans="1:9" ht="80" x14ac:dyDescent="0.15">
       <c r="A16"/>
       <c r="B16" s="60" t="s">
         <v>1221</v>
@@ -11935,7 +11935,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="165.75" customHeight="1">
+    <row r="17" spans="1:5" ht="165.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A17" s="6"/>
       <c r="B17" s="60" t="s">
         <v>1222</v>
@@ -11950,35 +11950,35 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A18" s="6"/>
       <c r="B18" s="60"/>
       <c r="C18" s="60"/>
       <c r="D18" s="60"/>
       <c r="E18" s="60"/>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A19" s="47"/>
       <c r="B19" s="30"/>
       <c r="C19" s="60"/>
       <c r="D19" s="60"/>
       <c r="E19" s="60"/>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A20" s="47"/>
       <c r="B20"/>
       <c r="C20" s="60"/>
       <c r="D20" s="60"/>
       <c r="E20" s="60"/>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A21" s="47"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="13" t="s">
         <v>406</v>
       </c>
@@ -11995,7 +11995,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="15"/>
       <c r="B23" s="12" t="s">
         <v>1179</v>
@@ -12010,7 +12010,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="13"/>
       <c r="B24" s="12" t="s">
         <v>134</v>
@@ -12025,7 +12025,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="13"/>
       <c r="B25" s="12"/>
       <c r="C25" s="12" t="s">
@@ -12036,64 +12036,64 @@
         <v>134</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="13"/>
       <c r="B26" s="12"/>
       <c r="C26" s="12"/>
       <c r="D26" s="12"/>
       <c r="E26" s="12"/>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="12"/>
       <c r="B27" s="12"/>
       <c r="C27" s="12"/>
       <c r="D27" s="12"/>
       <c r="E27" s="12"/>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="13"/>
       <c r="B28" s="12"/>
       <c r="C28" s="12"/>
       <c r="D28" s="12"/>
       <c r="E28" s="12"/>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="13"/>
       <c r="C29" s="12"/>
       <c r="D29" s="12"/>
       <c r="E29" s="12"/>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="13"/>
       <c r="C30" s="12"/>
       <c r="E30" s="12"/>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="13"/>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="13"/>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="13"/>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="13"/>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="13"/>
       <c r="B35" s="12"/>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="13"/>
       <c r="D36" s="12"/>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A37" s="13"/>
       <c r="C37" s="12"/>
       <c r="E37" s="12"/>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A38" s="13"/>
     </row>
   </sheetData>
@@ -12109,20 +12109,20 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:I36"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="37.375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="17.1640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="37.33203125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="61"/>
       <c r="B1" s="117"/>
       <c r="C1" s="117"/>
       <c r="D1" s="117"/>
       <c r="E1" s="117"/>
     </row>
-    <row r="2" spans="1:9" ht="15.75">
+    <row r="2" spans="1:9" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="9"/>
       <c r="B2" s="174" t="s">
         <v>1226</v>
@@ -12137,7 +12137,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
         <v>36</v>
       </c>
@@ -12154,7 +12154,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
         <v>38</v>
       </c>
@@ -12171,7 +12171,7 @@
         <v>1211</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>42</v>
       </c>
@@ -12188,7 +12188,7 @@
         <v>1230</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>48</v>
       </c>
@@ -12205,7 +12205,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="10" t="s">
         <v>534</v>
       </c>
@@ -12222,7 +12222,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="15.75" thickBot="1">
+    <row r="8" spans="1:9" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="10" t="s">
         <v>824</v>
       </c>
@@ -12239,7 +12239,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="9" spans="1:9" ht="195.75" thickBot="1">
+    <row r="9" spans="1:9" ht="209" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A9" s="20" t="s">
         <v>50</v>
       </c>
@@ -12256,7 +12256,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="135" t="s">
         <v>63</v>
       </c>
@@ -12273,7 +12273,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="136" t="s">
         <v>81</v>
       </c>
@@ -12294,7 +12294,7 @@
       <c r="H11" s="129"/>
       <c r="I11" s="129"/>
     </row>
-    <row r="12" spans="1:9" s="7" customFormat="1">
+    <row r="12" spans="1:9" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="102"/>
       <c r="B12" s="134" t="s">
         <v>1235</v>
@@ -12309,7 +12309,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="14"/>
       <c r="B13" s="116" t="s">
         <v>83</v>
@@ -12324,7 +12324,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="14" spans="1:9" s="49" customFormat="1" ht="68.25" customHeight="1">
+    <row r="14" spans="1:9" s="49" customFormat="1" ht="68.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A14" s="5" t="s">
         <v>84</v>
       </c>
@@ -12341,7 +12341,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="75">
+    <row r="15" spans="1:9" ht="64" x14ac:dyDescent="0.15">
       <c r="A15"/>
       <c r="B15" s="60" t="s">
         <v>1238</v>
@@ -12356,7 +12356,7 @@
         <v>1238</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="105">
+    <row r="16" spans="1:9" ht="96" x14ac:dyDescent="0.15">
       <c r="A16" s="6"/>
       <c r="B16" s="19" t="s">
         <v>1239</v>
@@ -12371,7 +12371,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="60">
+    <row r="17" spans="1:5" ht="64" x14ac:dyDescent="0.15">
       <c r="A17" s="6"/>
       <c r="B17" s="60" t="s">
         <v>1243</v>
@@ -12386,21 +12386,21 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A18" s="47"/>
       <c r="B18" s="60"/>
       <c r="C18" s="60"/>
       <c r="D18" s="60"/>
       <c r="E18" s="60"/>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
       <c r="A19" s="47"/>
       <c r="B19" s="60"/>
       <c r="C19" s="60"/>
       <c r="D19" s="60"/>
       <c r="E19" s="60"/>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A20" s="13" t="s">
         <v>406</v>
       </c>
@@ -12417,7 +12417,7 @@
         <v>1178</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A21" s="15"/>
       <c r="B21" s="12" t="s">
         <v>1179</v>
@@ -12432,7 +12432,7 @@
         <v>1179</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A22" s="13"/>
       <c r="B22" s="12" t="s">
         <v>1204</v>
@@ -12447,7 +12447,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A23" s="13"/>
       <c r="B23" s="12" t="s">
         <v>1245</v>
@@ -12462,7 +12462,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A24" s="13"/>
       <c r="B24" s="12" t="s">
         <v>1246</v>
@@ -12477,7 +12477,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A25" s="13"/>
       <c r="B25" s="12" t="s">
         <v>134</v>
@@ -12492,7 +12492,7 @@
         <v>413</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A26" s="12"/>
       <c r="B26" s="12" t="s">
         <v>146</v>
@@ -12507,7 +12507,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A27" s="13"/>
       <c r="B27" s="12" t="s">
         <v>147</v>
@@ -12522,7 +12522,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A28" s="13"/>
       <c r="C28" s="12" t="s">
         <v>147</v>
@@ -12532,34 +12532,34 @@
         <v>147</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A29" s="13"/>
       <c r="C29" s="12"/>
       <c r="E29" s="12"/>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A30" s="13"/>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A31" s="13"/>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A32" s="13"/>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A33" s="13"/>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A34" s="13"/>
       <c r="B34" s="12"/>
       <c r="D34" s="12"/>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A35" s="13"/>
       <c r="C35" s="12"/>
       <c r="E35" s="12"/>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A36" s="13"/>
     </row>
   </sheetData>
@@ -12572,7 +12572,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <sheetPr codeName="Sheet13"/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" verticalDpi="4294967293" r:id="rId1"/>
@@ -12586,40 +12586,40 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AP48"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="17.1640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.33203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="36.5" style="1" customWidth="1"/>
     <col min="4" max="4" width="45.5" style="1" customWidth="1"/>
-    <col min="5" max="5" width="43.125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="43.1640625" style="1" customWidth="1"/>
     <col min="6" max="8" width="36.5" style="1" customWidth="1"/>
-    <col min="9" max="9" width="44.25" style="1" customWidth="1"/>
+    <col min="9" max="9" width="44.1640625" style="1" customWidth="1"/>
     <col min="10" max="10" width="46" customWidth="1"/>
     <col min="11" max="12" width="38" customWidth="1"/>
     <col min="13" max="13" width="35" customWidth="1"/>
-    <col min="14" max="14" width="33.375" style="155" customWidth="1"/>
-    <col min="15" max="15" width="36.375" customWidth="1"/>
-    <col min="16" max="16" width="39.75" customWidth="1"/>
+    <col min="14" max="14" width="33.33203125" style="155" customWidth="1"/>
+    <col min="15" max="15" width="36.33203125" customWidth="1"/>
+    <col min="16" max="16" width="39.6640625" customWidth="1"/>
     <col min="17" max="17" width="36.5" style="1" customWidth="1"/>
-    <col min="18" max="18" width="37.375" style="1" customWidth="1"/>
+    <col min="18" max="18" width="37.33203125" style="1" customWidth="1"/>
     <col min="19" max="19" width="50" style="1" customWidth="1"/>
-    <col min="20" max="24" width="44.25" style="1" customWidth="1"/>
+    <col min="20" max="24" width="44.1640625" style="1" customWidth="1"/>
     <col min="25" max="25" width="50" style="1" customWidth="1"/>
     <col min="26" max="30" width="36.5" style="1" customWidth="1"/>
     <col min="31" max="31" width="38" customWidth="1"/>
-    <col min="32" max="32" width="33.375" customWidth="1"/>
-    <col min="33" max="34" width="47.875" customWidth="1"/>
-    <col min="35" max="35" width="39.75" customWidth="1"/>
+    <col min="32" max="32" width="33.33203125" customWidth="1"/>
+    <col min="33" max="34" width="47.83203125" customWidth="1"/>
+    <col min="35" max="35" width="39.6640625" customWidth="1"/>
     <col min="36" max="36" width="36.5" style="1" customWidth="1"/>
-    <col min="37" max="38" width="37.875" customWidth="1"/>
-    <col min="39" max="39" width="41.75" customWidth="1"/>
-    <col min="40" max="40" width="43.625" customWidth="1"/>
-    <col min="41" max="41" width="43.125" style="199" customWidth="1"/>
-    <col min="42" max="42" width="47.875" style="155" customWidth="1"/>
+    <col min="37" max="38" width="37.83203125" customWidth="1"/>
+    <col min="39" max="39" width="41.6640625" customWidth="1"/>
+    <col min="40" max="40" width="43.6640625" customWidth="1"/>
+    <col min="41" max="41" width="43.1640625" style="199" customWidth="1"/>
+    <col min="42" max="42" width="47.83203125" style="155" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42">
+    <row r="1" spans="1:42" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="8"/>
       <c r="B1" s="117" t="s">
         <v>150</v>
@@ -12739,7 +12739,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="2" spans="1:42" ht="15.75">
+    <row r="2" spans="1:42" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="9"/>
       <c r="B2" s="174" t="s">
         <v>187</v>
@@ -12865,7 +12865,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="3" spans="1:42" s="49" customFormat="1" ht="45">
+    <row r="3" spans="1:42" s="49" customFormat="1" ht="48" x14ac:dyDescent="0.15">
       <c r="A3" s="20" t="s">
         <v>36</v>
       </c>
@@ -12993,7 +12993,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="4" spans="1:42" s="49" customFormat="1" ht="30">
+    <row r="4" spans="1:42" s="49" customFormat="1" ht="32" x14ac:dyDescent="0.15">
       <c r="A4" s="20" t="s">
         <v>38</v>
       </c>
@@ -13121,7 +13121,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="5" spans="1:42" s="49" customFormat="1" ht="30">
+    <row r="5" spans="1:42" s="49" customFormat="1" ht="32" x14ac:dyDescent="0.15">
       <c r="A5" s="20" t="s">
         <v>42</v>
       </c>
@@ -13245,7 +13245,7 @@
         <v>258</v>
       </c>
     </row>
-    <row r="6" spans="1:42" s="49" customFormat="1" ht="15.75" thickBot="1">
+    <row r="6" spans="1:42" s="49" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A6" s="20" t="s">
         <v>48</v>
       </c>
@@ -13321,7 +13321,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="7" spans="1:42" ht="195.75" thickBot="1">
+    <row r="7" spans="1:42" ht="209" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A7" s="20" t="s">
         <v>50</v>
       </c>
@@ -13449,7 +13449,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="8" spans="1:42">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A8" s="141" t="s">
         <v>63</v>
       </c>
@@ -13569,7 +13569,7 @@
         <v>1120</v>
       </c>
     </row>
-    <row r="9" spans="1:42" s="255" customFormat="1">
+    <row r="9" spans="1:42" s="255" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="B9" s="255" t="s">
         <v>306</v>
       </c>
@@ -13694,7 +13694,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="10" spans="1:42" s="255" customFormat="1">
+    <row r="10" spans="1:42" s="255" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="B10" s="255" t="s">
         <v>307</v>
       </c>
@@ -13768,7 +13768,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="11" spans="1:42" s="255" customFormat="1">
+    <row r="11" spans="1:42" s="255" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="D11" s="255" t="s">
         <v>313</v>
       </c>
@@ -13794,7 +13794,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="12" spans="1:42" s="255" customFormat="1">
+    <row r="12" spans="1:42" s="255" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="D12" s="255" t="s">
         <v>317</v>
       </c>
@@ -13805,7 +13805,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="13" spans="1:42">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A13" s="251" t="s">
         <v>81</v>
       </c>
@@ -13933,7 +13933,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="14" spans="1:42" s="7" customFormat="1">
+    <row r="14" spans="1:42" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A14" s="97"/>
       <c r="B14" s="140" t="s">
         <v>319</v>
@@ -14053,7 +14053,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="15" spans="1:42">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A15" s="14"/>
       <c r="B15" s="116" t="s">
         <v>83</v>
@@ -14177,7 +14177,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="16" spans="1:42" s="49" customFormat="1" ht="75">
+    <row r="16" spans="1:42" s="49" customFormat="1" ht="80" x14ac:dyDescent="0.15">
       <c r="A16" s="5" t="s">
         <v>84</v>
       </c>
@@ -14305,7 +14305,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="17" spans="1:42" ht="60">
+    <row r="17" spans="1:42" ht="64" x14ac:dyDescent="0.2">
       <c r="B17" s="60" t="s">
         <v>328</v>
       </c>
@@ -14430,7 +14430,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="18" spans="1:42" s="49" customFormat="1" ht="180">
+    <row r="18" spans="1:42" s="49" customFormat="1" ht="192" x14ac:dyDescent="0.15">
       <c r="A18" s="6"/>
       <c r="B18" s="60" t="s">
         <v>342</v>
@@ -14556,7 +14556,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="19" spans="1:42" ht="135">
+    <row r="19" spans="1:42" ht="128" x14ac:dyDescent="0.15">
       <c r="A19" s="6"/>
       <c r="B19" s="60" t="s">
         <v>373</v>
@@ -14682,7 +14682,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="20" spans="1:42" ht="90">
+    <row r="20" spans="1:42" ht="96" x14ac:dyDescent="0.2">
       <c r="A20" s="47"/>
       <c r="B20" s="2"/>
       <c r="C20" s="2"/>
@@ -14762,7 +14762,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="21" spans="1:42" s="17" customFormat="1" ht="60">
+    <row r="21" spans="1:42" s="17" customFormat="1" ht="64" x14ac:dyDescent="0.15">
       <c r="A21" s="47"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -14808,7 +14808,7 @@
       <c r="AO21" s="197"/>
       <c r="AP21" s="154"/>
     </row>
-    <row r="22" spans="1:42" ht="30">
+    <row r="22" spans="1:42" ht="32" x14ac:dyDescent="0.2">
       <c r="A22" s="13" t="s">
         <v>406</v>
       </c>
@@ -14849,7 +14849,7 @@
       <c r="AJ22" s="2"/>
       <c r="AO22" s="197"/>
     </row>
-    <row r="23" spans="1:42">
+    <row r="23" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A23" s="13"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -14886,7 +14886,7 @@
       <c r="AO23" s="197"/>
       <c r="AP23" s="156"/>
     </row>
-    <row r="24" spans="1:42">
+    <row r="24" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A24" s="13"/>
       <c r="B24" s="104" t="s">
         <v>131</v>
@@ -15012,7 +15012,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="25" spans="1:42">
+    <row r="25" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A25" s="13"/>
       <c r="B25" s="104" t="s">
         <v>132</v>
@@ -15138,7 +15138,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="26" spans="1:42">
+    <row r="26" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A26" s="13"/>
       <c r="B26" s="104" t="s">
         <v>133</v>
@@ -15264,7 +15264,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="27" spans="1:42">
+    <row r="27" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A27" s="13"/>
       <c r="B27" s="12" t="s">
         <v>134</v>
@@ -15390,7 +15390,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="28" spans="1:42">
+    <row r="28" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A28" s="13"/>
       <c r="B28" s="12" t="s">
         <v>136</v>
@@ -15516,7 +15516,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="29" spans="1:42">
+    <row r="29" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A29" s="13"/>
       <c r="B29" s="12" t="s">
         <v>241</v>
@@ -15642,7 +15642,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="30" spans="1:42">
+    <row r="30" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A30" s="13"/>
       <c r="B30" s="12" t="s">
         <v>413</v>
@@ -15768,7 +15768,7 @@
         <v>417</v>
       </c>
     </row>
-    <row r="31" spans="1:42">
+    <row r="31" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A31" s="13"/>
       <c r="B31" s="12" t="s">
         <v>147</v>
@@ -15867,7 +15867,7 @@
         <v>407</v>
       </c>
     </row>
-    <row r="32" spans="1:42">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A32" s="13"/>
       <c r="D32" s="69" t="s">
         <v>413</v>
@@ -15945,7 +15945,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="33" spans="1:42">
+    <row r="33" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A33" s="13"/>
       <c r="C33" s="183" t="s">
         <v>149</v>
@@ -16032,7 +16032,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="34" spans="1:42">
+    <row r="34" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A34" s="13"/>
       <c r="C34" s="183" t="s">
         <v>146</v>
@@ -16121,7 +16121,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="35" spans="1:42">
+    <row r="35" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A35" s="13"/>
       <c r="B35" s="183" t="s">
         <v>149</v>
@@ -16196,7 +16196,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="36" spans="1:42">
+    <row r="36" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A36" s="13"/>
       <c r="B36" s="183" t="s">
         <v>146</v>
@@ -16245,7 +16245,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="37" spans="1:42">
+    <row r="37" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A37" s="13"/>
       <c r="B37" s="107" t="s">
         <v>425</v>
@@ -16284,7 +16284,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="38" spans="1:42">
+    <row r="38" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A38" s="13"/>
       <c r="B38" s="107" t="s">
         <v>426</v>
@@ -16328,7 +16328,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="39" spans="1:42">
+    <row r="39" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A39" s="13"/>
       <c r="D39" s="69"/>
       <c r="G39" s="69"/>
@@ -16359,7 +16359,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="40" spans="1:42">
+    <row r="40" spans="1:42" x14ac:dyDescent="0.2">
       <c r="F40" s="104"/>
       <c r="G40" s="69"/>
       <c r="Q40" s="104"/>
@@ -16379,7 +16379,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="41" spans="1:42">
+    <row r="41" spans="1:42" x14ac:dyDescent="0.2">
       <c r="F41" s="104"/>
       <c r="G41" s="69"/>
       <c r="Q41" s="104"/>
@@ -16391,7 +16391,7 @@
       <c r="W41"/>
       <c r="AI41" s="69"/>
     </row>
-    <row r="42" spans="1:42">
+    <row r="42" spans="1:42" x14ac:dyDescent="0.2">
       <c r="F42" s="12"/>
       <c r="G42" s="69"/>
       <c r="Q42" s="12"/>
@@ -16403,7 +16403,7 @@
       <c r="W42"/>
       <c r="AI42" s="69"/>
     </row>
-    <row r="43" spans="1:42">
+    <row r="43" spans="1:42" x14ac:dyDescent="0.2">
       <c r="F43" s="12"/>
       <c r="G43" s="69"/>
       <c r="Q43" s="12"/>
@@ -16414,7 +16414,7 @@
       <c r="AI43" s="69"/>
       <c r="AN43" s="1"/>
     </row>
-    <row r="44" spans="1:42">
+    <row r="44" spans="1:42" x14ac:dyDescent="0.2">
       <c r="F44" s="12"/>
       <c r="Q44" s="12"/>
       <c r="R44"/>
@@ -16422,23 +16422,23 @@
       <c r="AI44" s="69"/>
       <c r="AN44" s="1"/>
     </row>
-    <row r="45" spans="1:42">
+    <row r="45" spans="1:42" x14ac:dyDescent="0.2">
       <c r="F45" s="12"/>
       <c r="Q45" s="12"/>
       <c r="R45"/>
       <c r="AI45" s="69"/>
     </row>
-    <row r="46" spans="1:42">
+    <row r="46" spans="1:42" x14ac:dyDescent="0.2">
       <c r="F46" s="12"/>
       <c r="Q46" s="12"/>
       <c r="AI46" s="69"/>
     </row>
-    <row r="47" spans="1:42">
+    <row r="47" spans="1:42" x14ac:dyDescent="0.2">
       <c r="F47" s="12"/>
       <c r="Q47" s="12"/>
       <c r="AI47" s="72"/>
     </row>
-    <row r="48" spans="1:42">
+    <row r="48" spans="1:42" x14ac:dyDescent="0.2">
       <c r="F48" s="12"/>
       <c r="Q48" s="12"/>
     </row>
@@ -16455,44 +16455,44 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AR60"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="37.375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="17.1640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="37.33203125" style="1" customWidth="1"/>
     <col min="3" max="3" width="36.5" style="1" customWidth="1"/>
     <col min="4" max="5" width="45.5" style="1" customWidth="1"/>
     <col min="6" max="6" width="39.5" customWidth="1"/>
-    <col min="7" max="7" width="37.375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="37.33203125" style="1" customWidth="1"/>
     <col min="8" max="8" width="39.5" customWidth="1"/>
-    <col min="9" max="14" width="37.375" style="1" customWidth="1"/>
+    <col min="9" max="14" width="37.33203125" style="1" customWidth="1"/>
     <col min="15" max="16" width="36.5" style="1" customWidth="1"/>
-    <col min="17" max="18" width="37.375" style="1" customWidth="1"/>
-    <col min="19" max="19" width="50.75" customWidth="1"/>
-    <col min="20" max="20" width="47.875" customWidth="1"/>
-    <col min="21" max="21" width="37.375" style="1" customWidth="1"/>
+    <col min="17" max="18" width="37.33203125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="50.6640625" customWidth="1"/>
+    <col min="20" max="20" width="47.83203125" customWidth="1"/>
+    <col min="21" max="21" width="37.33203125" style="1" customWidth="1"/>
     <col min="22" max="22" width="45.5" style="1" customWidth="1"/>
-    <col min="23" max="23" width="42.25" style="1" customWidth="1"/>
+    <col min="23" max="23" width="42.1640625" style="1" customWidth="1"/>
     <col min="24" max="24" width="39.5" customWidth="1"/>
     <col min="25" max="25" width="45.5" style="1" customWidth="1"/>
-    <col min="26" max="27" width="37.375" style="1" customWidth="1"/>
+    <col min="26" max="27" width="37.33203125" style="1" customWidth="1"/>
     <col min="28" max="28" width="39.5" customWidth="1"/>
-    <col min="29" max="29" width="39.375" customWidth="1"/>
+    <col min="29" max="29" width="39.33203125" customWidth="1"/>
     <col min="30" max="30" width="37" customWidth="1"/>
     <col min="31" max="31" width="34.5" customWidth="1"/>
-    <col min="32" max="32" width="39.375" customWidth="1"/>
+    <col min="32" max="32" width="39.33203125" customWidth="1"/>
     <col min="33" max="33" width="45" customWidth="1"/>
-    <col min="34" max="34" width="38.25" customWidth="1"/>
+    <col min="34" max="34" width="38.1640625" customWidth="1"/>
     <col min="35" max="35" width="32" customWidth="1"/>
-    <col min="36" max="36" width="38.25" customWidth="1"/>
+    <col min="36" max="36" width="38.1640625" customWidth="1"/>
     <col min="37" max="37" width="50" style="1" customWidth="1"/>
-    <col min="38" max="38" width="36.375" customWidth="1"/>
-    <col min="39" max="39" width="34.875" customWidth="1"/>
-    <col min="40" max="40" width="37.375" style="1" customWidth="1"/>
+    <col min="38" max="38" width="36.33203125" customWidth="1"/>
+    <col min="39" max="39" width="34.83203125" customWidth="1"/>
+    <col min="40" max="40" width="37.33203125" style="1" customWidth="1"/>
     <col min="41" max="41" width="39.5" customWidth="1"/>
-    <col min="42" max="42" width="47.875" customWidth="1"/>
+    <col min="42" max="42" width="47.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:42">
+    <row r="1" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A1" s="61"/>
       <c r="B1" s="117" t="s">
         <v>428</v>
@@ -16616,7 +16616,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="2" spans="1:42" ht="15.75">
+    <row r="2" spans="1:42" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="9"/>
       <c r="B2" s="174" t="s">
         <v>467</v>
@@ -16742,7 +16742,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="3" spans="1:42" ht="30">
+    <row r="3" spans="1:42" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
         <v>36</v>
       </c>
@@ -16870,7 +16870,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="4" spans="1:42">
+    <row r="4" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
         <v>38</v>
       </c>
@@ -16998,7 +16998,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="5" spans="1:42" ht="30">
+    <row r="5" spans="1:42" ht="32" x14ac:dyDescent="0.2">
       <c r="A5" s="10" t="s">
         <v>42</v>
       </c>
@@ -17110,7 +17110,7 @@
       </c>
       <c r="AP5" s="50"/>
     </row>
-    <row r="6" spans="1:42">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A6" s="10" t="s">
         <v>48</v>
       </c>
@@ -17218,7 +17218,7 @@
       <c r="AO6" s="11"/>
       <c r="AP6" s="25"/>
     </row>
-    <row r="7" spans="1:42" ht="15.75" thickBot="1">
+    <row r="7" spans="1:42" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
         <v>534</v>
       </c>
@@ -17284,7 +17284,7 @@
       <c r="AO7" s="54"/>
       <c r="AP7" s="92"/>
     </row>
-    <row r="8" spans="1:42" ht="15.75" thickBot="1">
+    <row r="8" spans="1:42" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="100" t="s">
         <v>63</v>
       </c>
@@ -17386,7 +17386,7 @@
       </c>
       <c r="AP8" s="178"/>
     </row>
-    <row r="9" spans="1:42">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A9" s="260" t="s">
         <v>64</v>
       </c>
@@ -17555,7 +17555,7 @@
         <v>NORDEAML-872</v>
       </c>
     </row>
-    <row r="10" spans="1:42">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A10" s="260" t="s">
         <v>65</v>
       </c>
@@ -17724,7 +17724,7 @@
         <v>12140</v>
       </c>
     </row>
-    <row r="11" spans="1:42">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A11" s="260" t="s">
         <v>66</v>
       </c>
@@ -17852,7 +17852,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="12" spans="1:42">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A12" s="260" t="s">
         <v>66</v>
       </c>
@@ -17960,7 +17960,7 @@
       <c r="AO12" s="57"/>
       <c r="AP12" s="57"/>
     </row>
-    <row r="13" spans="1:42">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A13" s="260" t="s">
         <v>66</v>
       </c>
@@ -18028,7 +18028,7 @@
       <c r="AO13" s="57"/>
       <c r="AP13" s="57"/>
     </row>
-    <row r="14" spans="1:42">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A14" s="260" t="s">
         <v>66</v>
       </c>
@@ -18078,7 +18078,7 @@
       <c r="AO14" s="57"/>
       <c r="AP14" s="57"/>
     </row>
-    <row r="15" spans="1:42" s="263" customFormat="1" ht="14.25">
+    <row r="15" spans="1:42" s="263" customFormat="1" ht="14" x14ac:dyDescent="0.15">
       <c r="A15" s="262" t="s">
         <v>79</v>
       </c>
@@ -18176,7 +18176,7 @@
         <v>548</v>
       </c>
     </row>
-    <row r="16" spans="1:42" outlineLevel="1">
+    <row r="16" spans="1:42" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A16" s="136" t="s">
         <v>81</v>
       </c>
@@ -18304,7 +18304,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="17" spans="1:44" outlineLevel="1">
+    <row r="17" spans="1:44" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A17" s="97"/>
       <c r="B17" s="140" t="s">
         <v>556</v>
@@ -18432,7 +18432,7 @@
       <c r="AQ17" s="7"/>
       <c r="AR17" s="7"/>
     </row>
-    <row r="18" spans="1:44" s="7" customFormat="1" outlineLevel="1">
+    <row r="18" spans="1:44" s="7" customFormat="1" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A18" s="14"/>
       <c r="B18" s="116" t="s">
         <v>83</v>
@@ -18560,7 +18560,7 @@
       <c r="AQ18"/>
       <c r="AR18"/>
     </row>
-    <row r="19" spans="1:44" ht="90" outlineLevel="1">
+    <row r="19" spans="1:44" ht="96" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A19" s="5" t="s">
         <v>84</v>
       </c>
@@ -18690,7 +18690,7 @@
       <c r="AQ19" s="49"/>
       <c r="AR19" s="49"/>
     </row>
-    <row r="20" spans="1:44" s="49" customFormat="1" ht="60" outlineLevel="1">
+    <row r="20" spans="1:44" s="49" customFormat="1" ht="64" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A20"/>
       <c r="B20" s="60" t="s">
         <v>89</v>
@@ -18818,7 +18818,7 @@
       <c r="AQ20"/>
       <c r="AR20"/>
     </row>
-    <row r="21" spans="1:44" ht="165" outlineLevel="1">
+    <row r="21" spans="1:44" ht="176" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A21" s="6"/>
       <c r="B21" s="60" t="s">
         <v>589</v>
@@ -18944,7 +18944,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="22" spans="1:44" ht="135" outlineLevel="1">
+    <row r="22" spans="1:44" ht="144" outlineLevel="1" x14ac:dyDescent="0.15">
       <c r="A22" s="6"/>
       <c r="B22" s="60" t="s">
         <v>620</v>
@@ -19069,7 +19069,7 @@
       <c r="AP22" s="60"/>
       <c r="AR22" s="68"/>
     </row>
-    <row r="23" spans="1:44" ht="210" outlineLevel="1">
+    <row r="23" spans="1:44" ht="224" outlineLevel="1" x14ac:dyDescent="0.2">
       <c r="A23" s="47"/>
       <c r="B23" s="60" t="s">
         <v>652</v>
@@ -19148,7 +19148,7 @@
       </c>
       <c r="AP23" s="60"/>
     </row>
-    <row r="24" spans="1:44" ht="30">
+    <row r="24" spans="1:44" ht="32" x14ac:dyDescent="0.15">
       <c r="A24" s="6" t="s">
         <v>668</v>
       </c>
@@ -19317,7 +19317,7 @@
         <v>100% + Performance1 * Participation - Performance2</v>
       </c>
     </row>
-    <row r="25" spans="1:44" ht="30">
+    <row r="25" spans="1:44" ht="32" x14ac:dyDescent="0.15">
       <c r="A25" s="6" t="s">
         <v>669</v>
       </c>
@@ -19487,7 +19487,7 @@
       </c>
       <c r="AR25" s="68"/>
     </row>
-    <row r="26" spans="1:44">
+    <row r="26" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A26" s="47"/>
       <c r="C26" s="2"/>
       <c r="D26" s="2"/>
@@ -19523,7 +19523,7 @@
       <c r="AO26" s="2"/>
       <c r="AP26" s="60"/>
     </row>
-    <row r="27" spans="1:44">
+    <row r="27" spans="1:44" x14ac:dyDescent="0.15">
       <c r="A27" s="47"/>
       <c r="B27" s="2"/>
       <c r="C27" s="2"/>
@@ -19563,7 +19563,7 @@
       <c r="AO27" s="2"/>
       <c r="AP27" s="60"/>
     </row>
-    <row r="28" spans="1:44">
+    <row r="28" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A28" s="13" t="s">
         <v>406</v>
       </c>
@@ -19684,7 +19684,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="29" spans="1:44">
+    <row r="29" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A29"/>
       <c r="B29" s="104" t="s">
         <v>132</v>
@@ -19810,7 +19810,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="30" spans="1:44">
+    <row r="30" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A30" s="13"/>
       <c r="B30" s="104" t="s">
         <v>133</v>
@@ -19936,7 +19936,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="31" spans="1:44">
+    <row r="31" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A31" s="13"/>
       <c r="B31" s="12" t="s">
         <v>134</v>
@@ -20062,7 +20062,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="32" spans="1:44">
+    <row r="32" spans="1:44" x14ac:dyDescent="0.2">
       <c r="A32" s="13"/>
       <c r="B32" s="12" t="s">
         <v>135</v>
@@ -20188,7 +20188,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="33" spans="1:42">
+    <row r="33" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A33" s="13"/>
       <c r="B33" s="12" t="s">
         <v>241</v>
@@ -20314,7 +20314,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="34" spans="1:42">
+    <row r="34" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A34" s="12"/>
       <c r="B34" s="12" t="s">
         <v>265</v>
@@ -20440,7 +20440,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="35" spans="1:42">
+    <row r="35" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A35" s="13"/>
       <c r="B35" s="12" t="s">
         <v>146</v>
@@ -20560,7 +20560,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="36" spans="1:42">
+    <row r="36" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A36" s="13"/>
       <c r="B36" s="12" t="s">
         <v>147</v>
@@ -20664,7 +20664,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="37" spans="1:42">
+    <row r="37" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A37" s="13"/>
       <c r="B37" s="12"/>
       <c r="F37" s="12" t="s">
@@ -20740,7 +20740,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="38" spans="1:42">
+    <row r="38" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A38" s="13"/>
       <c r="F38" s="12"/>
       <c r="G38" s="12" t="s">
@@ -20793,7 +20793,7 @@
       </c>
       <c r="AP38" s="12"/>
     </row>
-    <row r="39" spans="1:42">
+    <row r="39" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A39" s="13"/>
       <c r="B39" s="183" t="s">
         <v>149</v>
@@ -20829,7 +20829,7 @@
       <c r="AN39" s="12"/>
       <c r="AP39" s="78"/>
     </row>
-    <row r="40" spans="1:42">
+    <row r="40" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A40" s="13"/>
       <c r="G40"/>
       <c r="H40" s="183" t="s">
@@ -20868,7 +20868,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="41" spans="1:42">
+    <row r="41" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A41" s="13"/>
       <c r="C41" s="183" t="s">
         <v>149</v>
@@ -20945,7 +20945,7 @@
       </c>
       <c r="AP41" s="78"/>
     </row>
-    <row r="42" spans="1:42">
+    <row r="42" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A42" s="13"/>
       <c r="G42"/>
       <c r="L42" s="12"/>
@@ -20977,7 +20977,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="43" spans="1:42">
+    <row r="43" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A43" s="13"/>
       <c r="G43"/>
       <c r="N43" s="12"/>
@@ -21001,7 +21001,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="44" spans="1:42">
+    <row r="44" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A44" s="13"/>
       <c r="B44" s="12"/>
       <c r="G44" s="12"/>
@@ -21028,7 +21028,7 @@
       </c>
       <c r="AN44" s="12"/>
     </row>
-    <row r="45" spans="1:42">
+    <row r="45" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A45" s="13"/>
       <c r="D45" s="104"/>
       <c r="E45" s="104"/>
@@ -21047,7 +21047,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="46" spans="1:42">
+    <row r="46" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D46" s="69"/>
       <c r="E46" s="69"/>
       <c r="G46"/>
@@ -21059,7 +21059,7 @@
       <c r="AK46"/>
       <c r="AM46" s="109"/>
     </row>
-    <row r="47" spans="1:42">
+    <row r="47" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G47"/>
       <c r="X47" s="1"/>
       <c r="AD47" s="72"/>
@@ -21068,7 +21068,7 @@
       <c r="AK47"/>
       <c r="AM47" s="1"/>
     </row>
-    <row r="48" spans="1:42">
+    <row r="48" spans="1:42" x14ac:dyDescent="0.2">
       <c r="G48"/>
       <c r="X48" s="1"/>
       <c r="AD48" s="72"/>
@@ -21077,14 +21077,14 @@
       <c r="AK48"/>
       <c r="AM48" s="1"/>
     </row>
-    <row r="49" spans="4:32">
+    <row r="49" spans="4:32" x14ac:dyDescent="0.2">
       <c r="G49"/>
       <c r="X49" s="1"/>
       <c r="Y49" s="12"/>
       <c r="AD49" s="72"/>
       <c r="AF49" s="19"/>
     </row>
-    <row r="50" spans="4:32">
+    <row r="50" spans="4:32" x14ac:dyDescent="0.2">
       <c r="D50" s="12"/>
       <c r="E50" s="12"/>
       <c r="V50" s="12"/>
@@ -21093,7 +21093,7 @@
       <c r="AD50" s="72"/>
       <c r="AF50" s="72"/>
     </row>
-    <row r="51" spans="4:32">
+    <row r="51" spans="4:32" x14ac:dyDescent="0.2">
       <c r="D51" s="12"/>
       <c r="E51" s="12"/>
       <c r="V51" s="12"/>
@@ -21102,31 +21102,31 @@
       <c r="AD51" s="72"/>
       <c r="AF51" s="72"/>
     </row>
-    <row r="52" spans="4:32">
+    <row r="52" spans="4:32" x14ac:dyDescent="0.2">
       <c r="D52" s="69"/>
       <c r="E52" s="69"/>
       <c r="V52" s="69"/>
       <c r="AD52" s="72"/>
       <c r="AF52" s="72"/>
     </row>
-    <row r="53" spans="4:32">
+    <row r="53" spans="4:32" x14ac:dyDescent="0.2">
       <c r="AD53" s="72"/>
     </row>
-    <row r="54" spans="4:32">
+    <row r="54" spans="4:32" x14ac:dyDescent="0.2">
       <c r="AD54" s="72"/>
     </row>
-    <row r="55" spans="4:32">
+    <row r="55" spans="4:32" x14ac:dyDescent="0.2">
       <c r="Y55" s="12"/>
       <c r="AD55" s="72"/>
     </row>
-    <row r="56" spans="4:32">
+    <row r="56" spans="4:32" x14ac:dyDescent="0.2">
       <c r="D56" s="12"/>
       <c r="E56" s="12"/>
       <c r="V56" s="12"/>
       <c r="Y56" s="69"/>
       <c r="AD56" s="72"/>
     </row>
-    <row r="57" spans="4:32">
+    <row r="57" spans="4:32" x14ac:dyDescent="0.2">
       <c r="D57" s="69"/>
       <c r="E57" s="69"/>
       <c r="V57" s="69"/>
@@ -21134,16 +21134,16 @@
       <c r="AC57" s="1"/>
       <c r="AD57" s="72"/>
     </row>
-    <row r="58" spans="4:32">
+    <row r="58" spans="4:32" x14ac:dyDescent="0.2">
       <c r="D58" s="69"/>
       <c r="E58" s="69"/>
       <c r="V58" s="69"/>
       <c r="AC58" s="104"/>
     </row>
-    <row r="59" spans="4:32">
+    <row r="59" spans="4:32" x14ac:dyDescent="0.2">
       <c r="AC59" s="69"/>
     </row>
-    <row r="60" spans="4:32">
+    <row r="60" spans="4:32" x14ac:dyDescent="0.2">
       <c r="AC60" s="1"/>
     </row>
   </sheetData>
@@ -21159,25 +21159,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:S44"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="17.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="37.375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="17.1640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="37.33203125" style="1" customWidth="1"/>
     <col min="4" max="5" width="38" customWidth="1"/>
-    <col min="6" max="6" width="37.375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="37.33203125" style="1" customWidth="1"/>
     <col min="7" max="9" width="38" customWidth="1"/>
-    <col min="10" max="10" width="37.125" style="155" customWidth="1"/>
-    <col min="11" max="11" width="34.625" customWidth="1"/>
-    <col min="12" max="12" width="37.375" style="1" customWidth="1"/>
-    <col min="13" max="13" width="34.625" customWidth="1"/>
-    <col min="14" max="14" width="47.875" customWidth="1"/>
-    <col min="15" max="15" width="37.375" style="1" customWidth="1"/>
+    <col min="10" max="10" width="37.1640625" style="155" customWidth="1"/>
+    <col min="11" max="11" width="34.6640625" customWidth="1"/>
+    <col min="12" max="12" width="37.33203125" style="1" customWidth="1"/>
+    <col min="13" max="13" width="34.6640625" customWidth="1"/>
+    <col min="14" max="14" width="47.83203125" customWidth="1"/>
+    <col min="15" max="15" width="37.33203125" style="1" customWidth="1"/>
     <col min="16" max="17" width="38" customWidth="1"/>
-    <col min="18" max="18" width="36.375" customWidth="1"/>
-    <col min="19" max="19" width="35.875" customWidth="1"/>
+    <col min="18" max="18" width="36.33203125" customWidth="1"/>
+    <col min="19" max="19" width="35.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" s="8"/>
       <c r="B1" s="117" t="s">
         <v>683</v>
@@ -21232,7 +21232,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="15.75">
+    <row r="2" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A2" s="9"/>
       <c r="B2" s="174" t="s">
         <v>700</v>
@@ -21289,7 +21289,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="30">
+    <row r="3" spans="1:19" ht="32" x14ac:dyDescent="0.2">
       <c r="A3" s="10" t="s">
         <v>36</v>
       </c>
@@ -21348,7 +21348,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="30">
+    <row r="4" spans="1:19" ht="32" x14ac:dyDescent="0.2">
       <c r="A4" s="10" t="s">
         <v>38</v>
       </c>
@@ -21407,7 +21407,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
+    <row r="5" spans="1:19" ht="16" x14ac:dyDescent="0.2">
       <c r="A5" s="74" t="s">
         <v>42</v>
       </c>
@@ -21466,7 +21466,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="15.75" thickBot="1">
+    <row r="6" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
         <v>48</v>
       </c>
@@ -21505,7 +21505,7 @@
       </c>
       <c r="S6" s="177"/>
     </row>
-    <row r="7" spans="1:19" ht="210.75" thickBot="1">
+    <row r="7" spans="1:19" ht="225" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A7" s="20" t="s">
         <v>50</v>
       </c>
@@ -21564,7 +21564,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="15.75" thickBot="1">
+    <row r="8" spans="1:19" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="135" t="s">
         <v>63</v>
       </c>
@@ -21623,7 +21623,7 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="9" spans="1:19">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" s="93"/>
       <c r="B9" s="57" t="s">
         <v>738</v>
@@ -21648,7 +21648,7 @@
       <c r="R9" s="57"/>
       <c r="S9" s="238"/>
     </row>
-    <row r="10" spans="1:19">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" s="93"/>
       <c r="B10" s="57" t="s">
         <v>307</v>
@@ -21673,7 +21673,7 @@
       <c r="R10" s="57"/>
       <c r="S10" s="238"/>
     </row>
-    <row r="11" spans="1:19">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" s="93"/>
       <c r="B11" s="57"/>
       <c r="C11" s="57"/>
@@ -21694,7 +21694,7 @@
       <c r="R11" s="57"/>
       <c r="S11" s="238"/>
     </row>
-    <row r="12" spans="1:19">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" s="93"/>
       <c r="B12" s="57"/>
       <c r="C12" s="57"/>
@@ -21715,7 +21715,7 @@
       <c r="R12" s="57"/>
       <c r="S12" s="238"/>
     </row>
-    <row r="13" spans="1:19">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="93"/>
       <c r="B13" s="57"/>
       <c r="C13" s="57"/>
@@ -21736,7 +21736,7 @@
       <c r="R13" s="57"/>
       <c r="S13" s="238"/>
     </row>
-    <row r="14" spans="1:19">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" s="136" t="s">
         <v>81</v>
       </c>
@@ -21795,7 +21795,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="15" spans="1:19" s="7" customFormat="1">
+    <row r="15" spans="1:19" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A15" s="97"/>
       <c r="B15" s="134" t="s">
         <v>556</v>
@@ -21852,7 +21852,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="16" spans="1:19">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="14"/>
       <c r="B16" s="77" t="s">
         <v>83</v>
@@ -21909,7 +21909,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="75">
+    <row r="17" spans="1:19" ht="80" x14ac:dyDescent="0.2">
       <c r="A17" s="5" t="s">
         <v>84</v>
       </c>
@@ -21968,7 +21968,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="18" spans="1:19" ht="60">
+    <row r="18" spans="1:19" ht="64" x14ac:dyDescent="0.15">
       <c r="A18"/>
       <c r="B18" s="60" t="s">
         <v>328</v>
@@ -22025,7 +22025,7 @@
         <v>328</v>
       </c>
     </row>
-    <row r="19" spans="1:19" ht="185.25" customHeight="1">
+    <row r="19" spans="1:19" ht="185.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A19" s="6"/>
       <c r="B19" s="60" t="s">
         <v>745</v>
@@ -22082,7 +22082,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="20" spans="1:19" ht="90">
+    <row r="20" spans="1:19" ht="96" x14ac:dyDescent="0.15">
       <c r="A20" s="6"/>
       <c r="B20" s="19" t="s">
         <v>760</v>
@@ -22139,7 +22139,7 @@
         <v>771</v>
       </c>
     </row>
-    <row r="21" spans="1:19" ht="90">
+    <row r="21" spans="1:19" ht="96" x14ac:dyDescent="0.15">
       <c r="A21" s="47"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -22164,7 +22164,7 @@
       <c r="R21" s="19"/>
       <c r="S21" s="2"/>
     </row>
-    <row r="22" spans="1:19" ht="45">
+    <row r="22" spans="1:19" ht="48" x14ac:dyDescent="0.15">
       <c r="A22" s="47"/>
       <c r="B22" s="2"/>
       <c r="C22" s="2"/>
@@ -22187,7 +22187,7 @@
       <c r="Q22" s="72"/>
       <c r="S22" s="2"/>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A23" s="47"/>
       <c r="B23" s="2"/>
       <c r="C23" s="2"/>
@@ -22206,7 +22206,7 @@
       <c r="Q23" s="72"/>
       <c r="S23" s="2"/>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24" s="13" t="s">
         <v>406</v>
       </c>
@@ -22265,7 +22265,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="25" spans="1:19">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25"/>
       <c r="B25" s="104" t="s">
         <v>132</v>
@@ -22322,7 +22322,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="26" spans="1:19">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" s="13"/>
       <c r="B26" s="104" t="s">
         <v>133</v>
@@ -22379,7 +22379,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="27" spans="1:19">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27" s="13"/>
       <c r="B27" s="12" t="s">
         <v>134</v>
@@ -22436,7 +22436,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="28" spans="1:19">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28" s="13"/>
       <c r="B28" s="12" t="s">
         <v>135</v>
@@ -22493,7 +22493,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="29" spans="1:19">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29" s="13"/>
       <c r="B29" s="12" t="s">
         <v>774</v>
@@ -22550,7 +22550,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="30" spans="1:19">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30" s="12"/>
       <c r="B30" s="12" t="s">
         <v>241</v>
@@ -22607,7 +22607,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="31" spans="1:19">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31" s="13"/>
       <c r="B31" s="69" t="s">
         <v>413</v>
@@ -22664,7 +22664,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="32" spans="1:19">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A32" s="13"/>
       <c r="B32" s="12" t="s">
         <v>147</v>
@@ -22698,7 +22698,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="33" spans="1:19">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A33" s="13"/>
       <c r="B33" s="12"/>
       <c r="E33" s="12" t="s">
@@ -22710,7 +22710,7 @@
       <c r="O33" s="12"/>
       <c r="P33" s="72"/>
     </row>
-    <row r="34" spans="1:19">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A34" s="13"/>
       <c r="B34" s="12"/>
       <c r="F34" s="69"/>
@@ -22722,7 +22722,7 @@
       <c r="P34" s="72"/>
       <c r="S34" s="1"/>
     </row>
-    <row r="35" spans="1:19">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A35" s="13"/>
       <c r="B35" s="183" t="s">
         <v>149</v>
@@ -22769,7 +22769,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="36" spans="1:19">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A36" s="13"/>
       <c r="B36" s="183" t="s">
         <v>146</v>
@@ -22820,7 +22820,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="37" spans="1:19">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A37" s="13"/>
       <c r="B37" s="107" t="s">
         <v>425</v>
@@ -22840,7 +22840,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="38" spans="1:19">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A38" s="13"/>
       <c r="B38" s="107" t="s">
         <v>426</v>
@@ -22861,7 +22861,7 @@
         <v>425</v>
       </c>
     </row>
-    <row r="39" spans="1:19">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A39" s="13"/>
       <c r="H39" s="108"/>
       <c r="J39" s="157"/>
@@ -22875,7 +22875,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="40" spans="1:19">
+    <row r="40" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A40" s="13"/>
       <c r="B40" s="12"/>
       <c r="K40" s="78"/>
@@ -22884,17 +22884,17 @@
         <v>425</v>
       </c>
     </row>
-    <row r="41" spans="1:19">
+    <row r="41" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A41" s="13"/>
       <c r="C41" s="12"/>
       <c r="O41" s="107" t="s">
         <v>426</v>
       </c>
     </row>
-    <row r="42" spans="1:19">
+    <row r="42" spans="1:19" x14ac:dyDescent="0.2">
       <c r="O42" s="109"/>
     </row>
-    <row r="44" spans="1:19">
+    <row r="44" spans="1:19" x14ac:dyDescent="0.2">
       <c r="F44" s="12"/>
       <c r="L44" s="12"/>
     </row>
@@ -22907,19 +22907,19 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:M42"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="114.875" customWidth="1"/>
+    <col min="1" max="1" width="114.83203125" customWidth="1"/>
     <col min="2" max="2" width="44" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="109" customWidth="1"/>
     <col min="5" max="5" width="51.5" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="38" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="35.875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="35.83203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="38" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="17.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="15">
+    <row r="1" spans="1:13" ht="16" x14ac:dyDescent="0.15">
       <c r="A1" s="2" t="s">
         <v>668</v>
       </c>
@@ -22933,7 +22933,7 @@
         <v>776</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="30">
+    <row r="2" spans="1:13" ht="32" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>589</v>
       </c>
@@ -22956,7 +22956,7 @@
         <v>779</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="30">
+    <row r="3" spans="1:13" ht="32" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>590</v>
       </c>
@@ -22979,7 +22979,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="30">
+    <row r="4" spans="1:13" ht="32" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
         <v>591</v>
       </c>
@@ -23002,7 +23002,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="30">
+    <row r="5" spans="1:13" ht="32" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>592</v>
       </c>
@@ -23025,7 +23025,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="45">
+    <row r="6" spans="1:13" ht="48" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
         <v>593</v>
       </c>
@@ -23048,7 +23048,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="28.5">
+    <row r="7" spans="1:13" ht="30" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
         <v>594</v>
       </c>
@@ -23074,7 +23074,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="30">
+    <row r="8" spans="1:13" ht="32" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
         <v>595</v>
       </c>
@@ -23097,7 +23097,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="45">
+    <row r="9" spans="1:13" ht="48" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
         <v>596</v>
       </c>
@@ -23117,7 +23117,7 @@
         <v>545</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="30">
+    <row r="10" spans="1:13" ht="32" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
         <v>597</v>
       </c>
@@ -23134,7 +23134,7 @@
         <v>789</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="51.75" customHeight="1">
+    <row r="11" spans="1:13" ht="51.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
         <v>598</v>
       </c>
@@ -23148,7 +23148,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="42.75">
+    <row r="12" spans="1:13" ht="45" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
         <v>599</v>
       </c>
@@ -23162,7 +23162,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="49.5" customHeight="1">
+    <row r="13" spans="1:13" ht="49.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
         <v>362</v>
       </c>
@@ -23176,7 +23176,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="30">
+    <row r="14" spans="1:13" ht="32" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
         <v>600</v>
       </c>
@@ -23190,7 +23190,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="30">
+    <row r="15" spans="1:13" ht="32" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
         <v>601</v>
       </c>
@@ -23204,7 +23204,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="30">
+    <row r="16" spans="1:13" ht="32" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
         <v>602</v>
       </c>
@@ -23218,7 +23218,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="30">
+    <row r="17" spans="1:12" ht="32" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
         <v>603</v>
       </c>
@@ -23232,7 +23232,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="45">
+    <row r="18" spans="1:12" ht="48" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
         <v>604</v>
       </c>
@@ -23246,7 +23246,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="45">
+    <row r="19" spans="1:12" ht="48" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
         <v>605</v>
       </c>
@@ -23260,7 +23260,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="86.25" customHeight="1">
+    <row r="20" spans="1:12" ht="86.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
         <v>606</v>
       </c>
@@ -23274,7 +23274,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="30">
+    <row r="21" spans="1:12" ht="32" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
         <v>607</v>
       </c>
@@ -23288,7 +23288,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="45">
+    <row r="22" spans="1:12" ht="48" x14ac:dyDescent="0.15">
       <c r="A22" s="2" t="s">
         <v>608</v>
       </c>
@@ -23302,7 +23302,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="45">
+    <row r="23" spans="1:12" ht="48" x14ac:dyDescent="0.15">
       <c r="A23" s="2" t="s">
         <v>609</v>
       </c>
@@ -23316,7 +23316,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="30">
+    <row r="24" spans="1:12" ht="32" x14ac:dyDescent="0.15">
       <c r="A24" s="90" t="s">
         <v>610</v>
       </c>
@@ -23333,7 +23333,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="30">
+    <row r="25" spans="1:12" ht="32" x14ac:dyDescent="0.15">
       <c r="A25" s="90" t="s">
         <v>611</v>
       </c>
@@ -23347,7 +23347,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="44.25" customHeight="1">
+    <row r="26" spans="1:12" ht="44.25" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A26" s="90" t="s">
         <v>612</v>
       </c>
@@ -23361,7 +23361,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="36.75" customHeight="1">
+    <row r="27" spans="1:12" ht="36.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A27" s="2" t="s">
         <v>613</v>
       </c>
@@ -23375,7 +23375,7 @@
         <v>778</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="30">
+    <row r="28" spans="1:12" ht="32" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
         <v>614</v>
       </c>
@@ -23389,7 +23389,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="45">
+    <row r="29" spans="1:12" ht="32" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
         <v>615</v>
       </c>
@@ -23403,7 +23403,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="30">
+    <row r="30" spans="1:12" ht="32" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="s">
         <v>348</v>
       </c>
@@ -23417,7 +23417,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="60">
+    <row r="31" spans="1:12" ht="64" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="s">
         <v>616</v>
       </c>
@@ -23431,7 +23431,7 @@
         <v>782</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="40.5" customHeight="1">
+    <row r="32" spans="1:12" ht="40.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="s">
         <v>617</v>
       </c>
@@ -23445,7 +23445,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="45">
+    <row r="33" spans="1:12" ht="48" x14ac:dyDescent="0.15">
       <c r="A33" s="2" t="s">
         <v>363</v>
       </c>
@@ -23462,7 +23462,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="60">
+    <row r="34" spans="1:12" ht="64" x14ac:dyDescent="0.15">
       <c r="A34" s="2" t="s">
         <v>618</v>
       </c>
@@ -23476,7 +23476,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="42.75">
+    <row r="35" spans="1:12" ht="45" x14ac:dyDescent="0.15">
       <c r="A35" s="2" t="s">
         <v>619</v>
       </c>
@@ -23490,7 +23490,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="28.5">
+    <row r="36" spans="1:12" ht="30" x14ac:dyDescent="0.15">
       <c r="D36" s="257" t="s">
         <v>379</v>
       </c>
@@ -23498,7 +23498,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="28.5">
+    <row r="37" spans="1:12" ht="30" x14ac:dyDescent="0.15">
       <c r="D37" s="257" t="s">
         <v>647</v>
       </c>
@@ -23506,7 +23506,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="28.5">
+    <row r="38" spans="1:12" ht="30" x14ac:dyDescent="0.15">
       <c r="D38" s="257" t="s">
         <v>648</v>
       </c>
@@ -23514,7 +23514,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="42.75">
+    <row r="39" spans="1:12" ht="45" x14ac:dyDescent="0.15">
       <c r="D39" s="257" t="s">
         <v>649</v>
       </c>
@@ -23522,7 +23522,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="28.5">
+    <row r="40" spans="1:12" ht="30" x14ac:dyDescent="0.15">
       <c r="D40" s="257" t="s">
         <v>650</v>
       </c>
@@ -23530,7 +23530,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="41" spans="1:12" ht="28.5">
+    <row r="41" spans="1:12" ht="30" x14ac:dyDescent="0.15">
       <c r="D41" s="257" t="s">
         <v>651</v>
       </c>
@@ -23538,7 +23538,7 @@
         <v>784</v>
       </c>
     </row>
-    <row r="42" spans="1:12">
+    <row r="42" spans="1:12" x14ac:dyDescent="0.15">
       <c r="D42" s="257"/>
     </row>
   </sheetData>
@@ -23558,15 +23558,15 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H44"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="16.375" style="7" customWidth="1"/>
-    <col min="2" max="2" width="42.75" style="7" customWidth="1"/>
-    <col min="3" max="8" width="39.125" style="7" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" style="7" customWidth="1"/>
+    <col min="2" max="2" width="42.6640625" style="7" customWidth="1"/>
+    <col min="3" max="8" width="39.1640625" style="7" customWidth="1"/>
     <col min="9" max="16384" width="9" style="7"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A1" s="22"/>
       <c r="B1" s="23" t="s">
         <v>797</v>
@@ -23590,7 +23590,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75">
+    <row r="2" spans="1:8" ht="17" x14ac:dyDescent="0.15">
       <c r="A2" s="24"/>
       <c r="B2" s="174" t="s">
         <v>804</v>
@@ -23614,7 +23614,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A3" s="20" t="s">
         <v>36</v>
       </c>
@@ -23640,7 +23640,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A4" s="20" t="s">
         <v>38</v>
       </c>
@@ -23666,7 +23666,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A5" s="20" t="s">
         <v>42</v>
       </c>
@@ -23692,7 +23692,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A6" s="20" t="s">
         <v>48</v>
       </c>
@@ -23718,7 +23718,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A7" s="20" t="s">
         <v>534</v>
       </c>
@@ -23736,7 +23736,7 @@
         <v>823</v>
       </c>
     </row>
-    <row r="8" spans="1:8" ht="15.75" thickBot="1">
+    <row r="8" spans="1:8" ht="16" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A8" s="20" t="s">
         <v>824</v>
       </c>
@@ -23750,7 +23750,7 @@
       </c>
       <c r="H8" s="25"/>
     </row>
-    <row r="9" spans="1:8" ht="236.25" customHeight="1" thickBot="1">
+    <row r="9" spans="1:8" ht="236.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A9" s="20" t="s">
         <v>50</v>
       </c>
@@ -23776,7 +23776,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="10" spans="1:8" customFormat="1" ht="24.75" customHeight="1" thickBot="1">
+    <row r="10" spans="1:8" customFormat="1" ht="24.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="141" t="s">
         <v>63</v>
       </c>
@@ -23802,7 +23802,7 @@
         <v>3100</v>
       </c>
     </row>
-    <row r="11" spans="1:8" customFormat="1">
+    <row r="11" spans="1:8" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="136" t="s">
         <v>81</v>
       </c>
@@ -23828,7 +23828,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="12" spans="1:8">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A12" s="102"/>
       <c r="B12" s="140" t="s">
         <v>832</v>
@@ -23852,7 +23852,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.15">
       <c r="A13" s="26"/>
       <c r="B13" s="27" t="s">
         <v>323</v>
@@ -23876,7 +23876,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="14" spans="1:8" ht="45">
+    <row r="14" spans="1:8" ht="48" x14ac:dyDescent="0.15">
       <c r="A14" s="21" t="s">
         <v>84</v>
       </c>
@@ -23902,7 +23902,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="15" spans="1:8" ht="90">
+    <row r="15" spans="1:8" ht="96" x14ac:dyDescent="0.15">
       <c r="B15" s="19" t="s">
         <v>835</v>
       </c>
@@ -23925,7 +23925,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="16" spans="1:8" ht="75">
+    <row r="16" spans="1:8" ht="80" x14ac:dyDescent="0.15">
       <c r="A16" s="21"/>
       <c r="B16" s="60" t="s">
         <v>838</v>
@@ -23949,7 +23949,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="165">
+    <row r="17" spans="1:8" ht="160" x14ac:dyDescent="0.15">
       <c r="B17" s="60" t="s">
         <v>841</v>
       </c>
@@ -23972,7 +23972,7 @@
         <v>846</v>
       </c>
     </row>
-    <row r="18" spans="1:8" s="2" customFormat="1" ht="151.5" customHeight="1">
+    <row r="18" spans="1:8" s="2" customFormat="1" ht="151.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="60"/>
       <c r="C18" s="60"/>
       <c r="D18" s="60"/>
@@ -23985,7 +23985,7 @@
       </c>
       <c r="H18" s="19"/>
     </row>
-    <row r="19" spans="1:8" s="2" customFormat="1" ht="60" customHeight="1">
+    <row r="19" spans="1:8" s="2" customFormat="1" ht="60" customHeight="1" x14ac:dyDescent="0.15">
       <c r="C19" s="30"/>
       <c r="D19" s="60"/>
       <c r="E19" s="60"/>
@@ -23993,10 +23993,10 @@
       <c r="G19" s="19"/>
       <c r="H19" s="60"/>
     </row>
-    <row r="20" spans="1:8" s="2" customFormat="1" ht="51" customHeight="1">
+    <row r="20" spans="1:8" s="2" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.15">
       <c r="G20" s="60"/>
     </row>
-    <row r="21" spans="1:8" s="2" customFormat="1">
+    <row r="21" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="13" t="s">
         <v>406</v>
       </c>
@@ -24022,7 +24022,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="22" spans="1:8" s="2" customFormat="1">
+    <row r="22" spans="1:8" s="2" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B22" s="104" t="s">
         <v>132</v>
       </c>
@@ -24045,7 +24045,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="23" spans="1:8" s="2" customFormat="1">
+    <row r="23" spans="1:8" s="2" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="B23" s="29" t="s">
         <v>133</v>
       </c>
@@ -24068,7 +24068,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="24" spans="1:8" s="44" customFormat="1">
+    <row r="24" spans="1:8" s="44" customFormat="1" x14ac:dyDescent="0.15">
       <c r="B24" s="46" t="s">
         <v>134</v>
       </c>
@@ -24091,7 +24091,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B25" s="46" t="s">
         <v>135</v>
       </c>
@@ -24114,7 +24114,7 @@
         <v>849</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B26" s="46" t="s">
         <v>682</v>
       </c>
@@ -24137,7 +24137,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B27" s="46" t="s">
         <v>850</v>
       </c>
@@ -24160,7 +24160,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="28" spans="1:8">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B28" s="46" t="s">
         <v>852</v>
       </c>
@@ -24183,7 +24183,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="29" spans="1:8">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B29" s="46" t="s">
         <v>857</v>
       </c>
@@ -24206,7 +24206,7 @@
         <v>854</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B30" s="46" t="s">
         <v>858</v>
       </c>
@@ -24229,7 +24229,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B31" s="46" t="s">
         <v>859</v>
       </c>
@@ -24252,7 +24252,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.15">
       <c r="B32" s="46" t="s">
         <v>147</v>
       </c>
@@ -24275,7 +24275,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="33" spans="3:8">
+    <row r="33" spans="3:8" x14ac:dyDescent="0.15">
       <c r="C33" s="31" t="s">
         <v>859</v>
       </c>
@@ -24295,7 +24295,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="34" spans="3:8">
+    <row r="34" spans="3:8" x14ac:dyDescent="0.15">
       <c r="C34" s="46" t="s">
         <v>147</v>
       </c>
@@ -24308,7 +24308,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="35" spans="3:8">
+    <row r="35" spans="3:8" x14ac:dyDescent="0.15">
       <c r="D35" s="46"/>
       <c r="E35" s="46"/>
       <c r="G35" s="46" t="s">
@@ -24316,31 +24316,31 @@
       </c>
       <c r="H35" s="46"/>
     </row>
-    <row r="36" spans="3:8">
+    <row r="36" spans="3:8" x14ac:dyDescent="0.15">
       <c r="D36" s="46"/>
       <c r="E36" s="46"/>
       <c r="G36" s="46"/>
       <c r="H36" s="46"/>
     </row>
-    <row r="37" spans="3:8">
+    <row r="37" spans="3:8" x14ac:dyDescent="0.15">
       <c r="C37" s="28" t="s">
         <v>860</v>
       </c>
     </row>
-    <row r="38" spans="3:8">
+    <row r="38" spans="3:8" x14ac:dyDescent="0.15">
       <c r="E38" s="46"/>
       <c r="G38" s="46"/>
       <c r="H38" s="46"/>
     </row>
-    <row r="39" spans="3:8">
+    <row r="39" spans="3:8" x14ac:dyDescent="0.15">
       <c r="F39" s="46"/>
     </row>
-    <row r="40" spans="3:8">
+    <row r="40" spans="3:8" x14ac:dyDescent="0.15">
       <c r="D40" s="28" t="s">
         <v>860</v>
       </c>
     </row>
-    <row r="43" spans="3:8">
+    <row r="43" spans="3:8" x14ac:dyDescent="0.15">
       <c r="E43" s="28" t="s">
         <v>860</v>
       </c>
@@ -24351,7 +24351,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="44" spans="3:8">
+    <row r="44" spans="3:8" x14ac:dyDescent="0.15">
       <c r="F44" s="28" t="s">
         <v>860</v>
       </c>
@@ -24369,21 +24369,21 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:M47"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="16.375" style="7" customWidth="1"/>
-    <col min="2" max="2" width="42.75" style="7" customWidth="1"/>
-    <col min="3" max="3" width="39.125" style="33" customWidth="1"/>
-    <col min="4" max="4" width="39.125" style="37" customWidth="1"/>
-    <col min="5" max="6" width="39.125" style="7" customWidth="1"/>
-    <col min="7" max="7" width="39.125" style="37" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" style="7" customWidth="1"/>
+    <col min="2" max="2" width="42.6640625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="39.1640625" style="33" customWidth="1"/>
+    <col min="4" max="4" width="39.1640625" style="37" customWidth="1"/>
+    <col min="5" max="6" width="39.1640625" style="7" customWidth="1"/>
+    <col min="7" max="7" width="39.1640625" style="37" customWidth="1"/>
     <col min="8" max="8" width="40" style="33" customWidth="1"/>
-    <col min="9" max="9" width="42.75" style="7" customWidth="1"/>
-    <col min="10" max="11" width="39.125" style="37" customWidth="1"/>
-    <col min="12" max="13" width="42.75" style="7" customWidth="1"/>
+    <col min="9" max="9" width="42.6640625" style="7" customWidth="1"/>
+    <col min="10" max="11" width="39.1640625" style="37" customWidth="1"/>
+    <col min="12" max="13" width="42.6640625" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A1" s="144" t="s">
         <v>861</v>
       </c>
@@ -24422,7 +24422,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A2" s="22"/>
       <c r="B2" s="23" t="s">
         <v>869</v>
@@ -24461,7 +24461,7 @@
         <v>880</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="15.75">
+    <row r="3" spans="1:13" ht="17" x14ac:dyDescent="0.15">
       <c r="A3" s="24"/>
       <c r="B3" s="174" t="s">
         <v>881</v>
@@ -24500,7 +24500,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A4" s="20" t="s">
         <v>36</v>
       </c>
@@ -24541,7 +24541,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A5" s="20" t="s">
         <v>38</v>
       </c>
@@ -24582,7 +24582,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A6" s="20" t="s">
         <v>42</v>
       </c>
@@ -24623,7 +24623,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="7" spans="1:13">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A7" s="20" t="s">
         <v>48</v>
       </c>
@@ -24664,7 +24664,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="15.75" thickBot="1">
+    <row r="8" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A8" s="20" t="s">
         <v>534</v>
       </c>
@@ -24687,7 +24687,7 @@
       <c r="L8" s="25"/>
       <c r="M8" s="25"/>
     </row>
-    <row r="9" spans="1:13" ht="275.25" customHeight="1" thickBot="1">
+    <row r="9" spans="1:13" ht="275.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A9" s="20" t="s">
         <v>50</v>
       </c>
@@ -24728,7 +24728,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="15.75" thickBot="1">
+    <row r="10" spans="1:13" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="141" t="s">
         <v>63</v>
       </c>
@@ -24769,7 +24769,7 @@
         <v>3100</v>
       </c>
     </row>
-    <row r="11" spans="1:13">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A11" s="136" t="s">
         <v>81</v>
       </c>
@@ -24810,7 +24810,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="12" spans="1:13" s="7" customFormat="1">
+    <row r="12" spans="1:13" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="102"/>
       <c r="B12" s="140" t="s">
         <v>832</v>
@@ -24849,7 +24849,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="13" spans="1:13">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A13" s="43"/>
       <c r="B13" s="27" t="s">
         <v>323</v>
@@ -24888,7 +24888,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="45">
+    <row r="14" spans="1:13" ht="48" x14ac:dyDescent="0.15">
       <c r="A14" s="21" t="s">
         <v>84</v>
       </c>
@@ -24929,7 +24929,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="90">
+    <row r="15" spans="1:13" ht="96" x14ac:dyDescent="0.15">
       <c r="A15"/>
       <c r="B15" s="19" t="s">
         <v>835</v>
@@ -24968,7 +24968,7 @@
         <v>835</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="108.75" customHeight="1">
+    <row r="16" spans="1:13" ht="108.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="169"/>
       <c r="B16" s="60" t="s">
         <v>612</v>
@@ -25007,7 +25007,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="120">
+    <row r="17" spans="1:13" ht="128" x14ac:dyDescent="0.15">
       <c r="A17" s="21"/>
       <c r="B17" s="60" t="s">
         <v>917</v>
@@ -25046,7 +25046,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="18" spans="1:13" ht="144.75" customHeight="1">
+    <row r="18" spans="1:13" ht="144.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="B18" s="60" t="s">
         <v>926</v>
       </c>
@@ -25078,7 +25078,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="19" spans="1:13">
+    <row r="19" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A19" s="2"/>
       <c r="B19" s="30"/>
       <c r="C19" s="30"/>
@@ -25090,7 +25090,7 @@
       <c r="L19" s="30"/>
       <c r="M19" s="30"/>
     </row>
-    <row r="20" spans="1:13">
+    <row r="20" spans="1:13" x14ac:dyDescent="0.15">
       <c r="A20" s="2"/>
       <c r="B20" s="2"/>
       <c r="C20" s="30"/>
@@ -25105,7 +25105,7 @@
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
     </row>
-    <row r="21" spans="1:13">
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A21" s="13" t="s">
         <v>406</v>
       </c>
@@ -25146,7 +25146,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="22" spans="1:13">
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
       <c r="A22" s="2"/>
       <c r="B22" s="104" t="s">
         <v>132</v>
@@ -25185,7 +25185,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="23" spans="1:13">
+    <row r="23" spans="1:13" ht="16" x14ac:dyDescent="0.15">
       <c r="A23" s="2"/>
       <c r="B23" s="29" t="s">
         <v>133</v>
@@ -25224,7 +25224,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="24" spans="1:13" s="17" customFormat="1">
+    <row r="24" spans="1:13" s="17" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A24" s="44"/>
       <c r="B24" s="31" t="s">
         <v>134</v>
@@ -25263,7 +25263,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="25" spans="1:13">
+    <row r="25" spans="1:13" x14ac:dyDescent="0.15">
       <c r="B25" s="46" t="s">
         <v>135</v>
       </c>
@@ -25301,7 +25301,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="26" spans="1:13">
+    <row r="26" spans="1:13" x14ac:dyDescent="0.15">
       <c r="B26" s="31" t="s">
         <v>674</v>
       </c>
@@ -25339,7 +25339,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="27" spans="1:13">
+    <row r="27" spans="1:13" x14ac:dyDescent="0.15">
       <c r="B27" s="31" t="s">
         <v>409</v>
       </c>
@@ -25377,7 +25377,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="28" spans="1:13">
+    <row r="28" spans="1:13" x14ac:dyDescent="0.15">
       <c r="B28" s="31" t="s">
         <v>852</v>
       </c>
@@ -25415,7 +25415,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="29" spans="1:13">
+    <row r="29" spans="1:13" x14ac:dyDescent="0.15">
       <c r="B29" s="31" t="s">
         <v>857</v>
       </c>
@@ -25453,7 +25453,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:13" x14ac:dyDescent="0.15">
       <c r="B30" s="31" t="s">
         <v>148</v>
       </c>
@@ -25491,7 +25491,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="31" spans="1:13">
+    <row r="31" spans="1:13" x14ac:dyDescent="0.15">
       <c r="B31" s="31" t="s">
         <v>858</v>
       </c>
@@ -25527,7 +25527,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="32" spans="1:13">
+    <row r="32" spans="1:13" x14ac:dyDescent="0.15">
       <c r="B32" s="46" t="s">
         <v>859</v>
       </c>
@@ -25560,7 +25560,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="33" spans="2:13">
+    <row r="33" spans="2:13" x14ac:dyDescent="0.15">
       <c r="B33" s="31" t="s">
         <v>147</v>
       </c>
@@ -25592,7 +25592,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="34" spans="2:13">
+    <row r="34" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C34" s="31" t="s">
         <v>859</v>
       </c>
@@ -25610,7 +25610,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="35" spans="2:13">
+    <row r="35" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C35" s="31" t="s">
         <v>147</v>
       </c>
@@ -25622,12 +25622,12 @@
         <v>147</v>
       </c>
     </row>
-    <row r="36" spans="2:13">
+    <row r="36" spans="2:13" x14ac:dyDescent="0.15">
       <c r="G36" s="31"/>
       <c r="H36" s="45"/>
       <c r="K36" s="33"/>
     </row>
-    <row r="37" spans="2:13">
+    <row r="37" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C37" s="37"/>
       <c r="D37" s="38"/>
       <c r="F37" s="46"/>
@@ -25636,12 +25636,12 @@
         <v>860</v>
       </c>
     </row>
-    <row r="38" spans="2:13">
+    <row r="38" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C38" s="37"/>
       <c r="H38" s="31"/>
       <c r="I38" s="29"/>
     </row>
-    <row r="39" spans="2:13">
+    <row r="39" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C39" s="37"/>
       <c r="E39" s="28" t="s">
         <v>860</v>
@@ -25649,44 +25649,44 @@
       <c r="H39" s="31"/>
       <c r="I39" s="46"/>
     </row>
-    <row r="40" spans="2:13">
+    <row r="40" spans="2:13" x14ac:dyDescent="0.15">
       <c r="C40" s="38" t="s">
         <v>860</v>
       </c>
       <c r="H40" s="31"/>
       <c r="I40" s="46"/>
     </row>
-    <row r="41" spans="2:13">
+    <row r="41" spans="2:13" x14ac:dyDescent="0.15">
       <c r="G41" s="38" t="s">
         <v>860</v>
       </c>
       <c r="H41" s="31"/>
       <c r="I41" s="46"/>
     </row>
-    <row r="42" spans="2:13">
+    <row r="42" spans="2:13" x14ac:dyDescent="0.15">
       <c r="F42" s="28" t="s">
         <v>860</v>
       </c>
       <c r="H42" s="31"/>
       <c r="I42" s="46"/>
     </row>
-    <row r="43" spans="2:13">
+    <row r="43" spans="2:13" x14ac:dyDescent="0.15">
       <c r="H43" s="31"/>
       <c r="I43" s="46"/>
     </row>
-    <row r="44" spans="2:13">
+    <row r="44" spans="2:13" x14ac:dyDescent="0.15">
       <c r="H44" s="31"/>
       <c r="I44" s="46"/>
     </row>
-    <row r="45" spans="2:13">
+    <row r="45" spans="2:13" x14ac:dyDescent="0.15">
       <c r="H45" s="31"/>
       <c r="I45" s="46"/>
     </row>
-    <row r="46" spans="2:13">
+    <row r="46" spans="2:13" x14ac:dyDescent="0.15">
       <c r="H46" s="31"/>
       <c r="I46" s="46"/>
     </row>
-    <row r="47" spans="2:13">
+    <row r="47" spans="2:13" x14ac:dyDescent="0.15">
       <c r="I47" s="46"/>
     </row>
   </sheetData>
@@ -25702,25 +25702,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:Z51"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.375" style="7" customWidth="1"/>
-    <col min="2" max="4" width="32.625" style="7" customWidth="1"/>
-    <col min="5" max="6" width="32.625" style="37" customWidth="1"/>
-    <col min="7" max="9" width="32.625" style="7" customWidth="1"/>
-    <col min="10" max="10" width="32.625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="32.625" style="37" customWidth="1"/>
-    <col min="12" max="13" width="32.625" style="1" customWidth="1"/>
-    <col min="14" max="17" width="32.625" style="33" customWidth="1"/>
-    <col min="18" max="20" width="32.625" style="1" customWidth="1"/>
-    <col min="21" max="21" width="32.625" style="33" customWidth="1"/>
-    <col min="22" max="23" width="32.625" style="7" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" style="7" customWidth="1"/>
+    <col min="2" max="4" width="32.6640625" style="7" customWidth="1"/>
+    <col min="5" max="6" width="32.6640625" style="37" customWidth="1"/>
+    <col min="7" max="9" width="32.6640625" style="7" customWidth="1"/>
+    <col min="10" max="10" width="32.6640625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="32.6640625" style="37" customWidth="1"/>
+    <col min="12" max="13" width="32.6640625" style="1" customWidth="1"/>
+    <col min="14" max="17" width="32.6640625" style="33" customWidth="1"/>
+    <col min="18" max="20" width="32.6640625" style="1" customWidth="1"/>
+    <col min="21" max="21" width="32.6640625" style="33" customWidth="1"/>
+    <col min="22" max="23" width="32.6640625" style="7" customWidth="1"/>
     <col min="24" max="24" width="9" customWidth="1"/>
-    <col min="25" max="25" width="6.375" customWidth="1"/>
-    <col min="26" max="26" width="7.875" customWidth="1"/>
+    <col min="25" max="25" width="6.33203125" customWidth="1"/>
+    <col min="26" max="26" width="7.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A1" s="22"/>
       <c r="B1" s="23"/>
       <c r="C1" s="23" t="s">
@@ -25787,7 +25787,7 @@
         <v>953</v>
       </c>
     </row>
-    <row r="2" spans="1:26" ht="15.75">
+    <row r="2" spans="1:26" ht="17" x14ac:dyDescent="0.15">
       <c r="A2" s="24"/>
       <c r="B2" s="227" t="s">
         <v>954</v>
@@ -25856,7 +25856,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:26" ht="16" x14ac:dyDescent="0.15">
       <c r="A3" s="20" t="s">
         <v>36</v>
       </c>
@@ -25927,7 +25927,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:26" ht="16" x14ac:dyDescent="0.15">
       <c r="A4" s="20" t="s">
         <v>38</v>
       </c>
@@ -25998,7 +25998,7 @@
         <v>895</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:26" x14ac:dyDescent="0.15">
       <c r="A5" s="20" t="s">
         <v>42</v>
       </c>
@@ -26069,7 +26069,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="6" spans="1:26" ht="45">
+    <row r="6" spans="1:26" ht="48" x14ac:dyDescent="0.15">
       <c r="A6" s="20" t="s">
         <v>48</v>
       </c>
@@ -26138,7 +26138,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:26" ht="16" x14ac:dyDescent="0.15">
       <c r="A7" s="20"/>
       <c r="B7" s="25"/>
       <c r="C7" s="25"/>
@@ -26171,7 +26171,7 @@
       <c r="V7" s="25"/>
       <c r="W7" s="25"/>
     </row>
-    <row r="8" spans="1:26" ht="15.75" thickBot="1">
+    <row r="8" spans="1:26" ht="17" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A8" s="20" t="s">
         <v>534</v>
       </c>
@@ -26220,7 +26220,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="9" spans="1:26" ht="12.75" customHeight="1" thickBot="1">
+    <row r="9" spans="1:26" ht="12.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A9" s="20" t="s">
         <v>50</v>
       </c>
@@ -26291,7 +26291,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="10" spans="1:26" ht="15.75" thickBot="1">
+    <row r="10" spans="1:26" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="141" t="s">
         <v>63</v>
       </c>
@@ -26362,7 +26362,7 @@
         <v>3100</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A11" s="136" t="s">
         <v>81</v>
       </c>
@@ -26433,7 +26433,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="12" spans="1:26" s="7" customFormat="1">
+    <row r="12" spans="1:26" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A12" s="102"/>
       <c r="B12" s="140" t="s">
         <v>832</v>
@@ -26502,7 +26502,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A13" s="26"/>
       <c r="B13" s="36" t="s">
         <v>323</v>
@@ -26571,7 +26571,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="14" spans="1:26" ht="60">
+    <row r="14" spans="1:26" ht="64" x14ac:dyDescent="0.15">
       <c r="A14" s="21" t="s">
         <v>84</v>
       </c>
@@ -26642,7 +26642,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="15" spans="1:26" ht="120">
+    <row r="15" spans="1:26" ht="112" x14ac:dyDescent="0.15">
       <c r="A15" s="223"/>
       <c r="B15" s="19" t="s">
         <v>835</v>
@@ -26711,7 +26711,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="16" spans="1:26" ht="145.5" customHeight="1">
+    <row r="16" spans="1:26" ht="145.5" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A16" s="228"/>
       <c r="B16" s="211" t="s">
         <v>1012</v>
@@ -26781,7 +26781,7 @@
       </c>
       <c r="Z16" s="19"/>
     </row>
-    <row r="17" spans="1:23" ht="165">
+    <row r="17" spans="1:23" ht="160" x14ac:dyDescent="0.15">
       <c r="A17" s="234"/>
       <c r="B17" s="213" t="s">
         <v>919</v>
@@ -26850,7 +26850,7 @@
         <v>1027</v>
       </c>
     </row>
-    <row r="18" spans="1:23" ht="150">
+    <row r="18" spans="1:23" ht="160" x14ac:dyDescent="0.15">
       <c r="A18" s="231"/>
       <c r="B18" s="218" t="s">
         <v>928</v>
@@ -26915,7 +26915,7 @@
       </c>
       <c r="W18" s="30"/>
     </row>
-    <row r="19" spans="1:23">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.15">
       <c r="A19" s="2"/>
       <c r="B19" s="30"/>
       <c r="C19" s="30"/>
@@ -26939,7 +26939,7 @@
       <c r="U19" s="30"/>
       <c r="V19" s="30"/>
     </row>
-    <row r="20" spans="1:23">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A20" s="2"/>
       <c r="B20" s="60"/>
       <c r="C20" s="60"/>
@@ -26958,7 +26958,7 @@
       <c r="V20" s="60"/>
       <c r="W20" s="60"/>
     </row>
-    <row r="21" spans="1:23">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A21" s="2"/>
       <c r="B21" s="2"/>
       <c r="C21" s="2"/>
@@ -26977,7 +26977,7 @@
       <c r="V21" s="2"/>
       <c r="W21" s="2"/>
     </row>
-    <row r="22" spans="1:23">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A22" s="13" t="s">
         <v>406</v>
       </c>
@@ -27048,7 +27048,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="23" spans="1:23">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A23" s="2"/>
       <c r="B23" s="104" t="s">
         <v>132</v>
@@ -27117,7 +27117,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="24" spans="1:23" s="17" customFormat="1">
+    <row r="24" spans="1:23" s="17" customFormat="1" ht="16" x14ac:dyDescent="0.15">
       <c r="A24" s="44"/>
       <c r="B24" s="45" t="s">
         <v>133</v>
@@ -27186,7 +27186,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="25" spans="1:23">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.15">
       <c r="B25" s="31" t="s">
         <v>134</v>
       </c>
@@ -27254,7 +27254,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="26" spans="1:23">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.15">
       <c r="B26" s="46" t="s">
         <v>135</v>
       </c>
@@ -27322,7 +27322,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="27" spans="1:23">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.15">
       <c r="B27" s="31" t="s">
         <v>674</v>
       </c>
@@ -27390,7 +27390,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="28" spans="1:23">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.15">
       <c r="B28" s="46" t="s">
         <v>410</v>
       </c>
@@ -27458,7 +27458,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="29" spans="1:23">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.15">
       <c r="B29" s="31" t="s">
         <v>408</v>
       </c>
@@ -27526,7 +27526,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="30" spans="1:23">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B30" s="31" t="s">
         <v>854</v>
       </c>
@@ -27594,7 +27594,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="31" spans="1:23">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B31" s="31" t="s">
         <v>852</v>
       </c>
@@ -27662,7 +27662,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="32" spans="1:23">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B32" s="31" t="s">
         <v>857</v>
       </c>
@@ -27730,7 +27730,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="33" spans="2:23">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.15">
       <c r="B33" s="31" t="s">
         <v>148</v>
       </c>
@@ -27792,7 +27792,7 @@
       <c r="V33" s="46"/>
       <c r="W33" s="46"/>
     </row>
-    <row r="34" spans="2:23">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.15">
       <c r="B34" s="31" t="s">
         <v>858</v>
       </c>
@@ -27860,7 +27860,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="35" spans="2:23">
+    <row r="35" spans="2:23" x14ac:dyDescent="0.15">
       <c r="B35" s="31" t="s">
         <v>859</v>
       </c>
@@ -27920,7 +27920,7 @@
       </c>
       <c r="U35" s="34"/>
     </row>
-    <row r="36" spans="2:23">
+    <row r="36" spans="2:23" x14ac:dyDescent="0.15">
       <c r="B36" s="31" t="s">
         <v>147</v>
       </c>
@@ -27966,7 +27966,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="37" spans="2:23">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.15">
       <c r="D37" s="7" t="s">
         <v>1034</v>
       </c>
@@ -28018,7 +28018,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="38" spans="2:23">
+    <row r="38" spans="2:23" ht="16" x14ac:dyDescent="0.15">
       <c r="B38" s="7" t="s">
         <v>1034</v>
       </c>
@@ -28060,7 +28060,7 @@
         <v>860</v>
       </c>
     </row>
-    <row r="39" spans="2:23">
+    <row r="39" spans="2:23" ht="16" x14ac:dyDescent="0.15">
       <c r="G39" s="46"/>
       <c r="H39" s="46"/>
       <c r="J39" t="s">
@@ -28095,7 +28095,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="40" spans="2:23">
+    <row r="40" spans="2:23" x14ac:dyDescent="0.15">
       <c r="B40" s="46"/>
       <c r="C40" s="46"/>
       <c r="J40"/>
@@ -28109,7 +28109,7 @@
       <c r="S40"/>
       <c r="T40"/>
     </row>
-    <row r="41" spans="2:23">
+    <row r="41" spans="2:23" x14ac:dyDescent="0.15">
       <c r="J41"/>
       <c r="L41" t="s">
         <v>1034</v>
@@ -28131,7 +28131,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="42" spans="2:23">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="J42"/>
       <c r="L42"/>
       <c r="M42"/>
@@ -28145,13 +28145,13 @@
         <v>860</v>
       </c>
     </row>
-    <row r="43" spans="2:23">
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="N43" s="31"/>
       <c r="O43" s="31"/>
       <c r="P43" s="31"/>
       <c r="Q43" s="31"/>
     </row>
-    <row r="44" spans="2:23">
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="G44" s="28" t="s">
         <v>860</v>
       </c>
@@ -28163,7 +28163,7 @@
       <c r="P44" s="31"/>
       <c r="Q44" s="31"/>
     </row>
-    <row r="45" spans="2:23">
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B45" s="28" t="s">
         <v>860</v>
       </c>
@@ -28178,34 +28178,34 @@
       <c r="P45" s="31"/>
       <c r="Q45" s="31"/>
     </row>
-    <row r="46" spans="2:23">
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="N46" s="31"/>
       <c r="O46" s="31"/>
       <c r="P46" s="31"/>
       <c r="Q46" s="31"/>
     </row>
-    <row r="47" spans="2:23">
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="N47" s="31"/>
       <c r="O47" s="31"/>
       <c r="P47" s="31"/>
       <c r="Q47" s="31"/>
     </row>
-    <row r="48" spans="2:23">
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="N48" s="31"/>
       <c r="O48" s="31"/>
       <c r="P48" s="31"/>
       <c r="Q48" s="31"/>
     </row>
-    <row r="49" spans="15:17">
+    <row r="49" spans="15:17" x14ac:dyDescent="0.2">
       <c r="O49" s="31"/>
       <c r="P49" s="31"/>
       <c r="Q49" s="31"/>
     </row>
-    <row r="50" spans="15:17">
+    <row r="50" spans="15:17" x14ac:dyDescent="0.2">
       <c r="P50" s="31"/>
       <c r="Q50" s="31"/>
     </row>
-    <row r="51" spans="15:17">
+    <row r="51" spans="15:17" x14ac:dyDescent="0.2">
       <c r="P51" s="31"/>
       <c r="Q51" s="31"/>
     </row>
@@ -28222,18 +28222,18 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R70"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="16.375" style="7" customWidth="1"/>
-    <col min="2" max="2" width="42.75" style="7" customWidth="1"/>
-    <col min="3" max="3" width="39.125" style="37" customWidth="1"/>
-    <col min="4" max="12" width="39.125" style="33" customWidth="1"/>
-    <col min="13" max="14" width="39.125" style="37" customWidth="1"/>
-    <col min="15" max="15" width="39.125" style="33" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" style="7" customWidth="1"/>
+    <col min="2" max="2" width="42.6640625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="39.1640625" style="37" customWidth="1"/>
+    <col min="4" max="12" width="39.1640625" style="33" customWidth="1"/>
+    <col min="13" max="14" width="39.1640625" style="37" customWidth="1"/>
+    <col min="15" max="15" width="39.1640625" style="33" customWidth="1"/>
     <col min="16" max="18" width="37" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:18" ht="16" x14ac:dyDescent="0.15">
       <c r="A1" s="22"/>
       <c r="B1" s="23" t="s">
         <v>1035</v>
@@ -28287,7 +28287,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="2" spans="1:18" ht="15.75">
+    <row r="2" spans="1:18" ht="17" x14ac:dyDescent="0.15">
       <c r="A2" s="24"/>
       <c r="B2" s="174" t="s">
         <v>1052</v>
@@ -28341,7 +28341,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A3" s="20" t="s">
         <v>36</v>
       </c>
@@ -28397,7 +28397,7 @@
         <v>1072</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A4" s="20" t="s">
         <v>38</v>
       </c>
@@ -28453,7 +28453,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A5" s="20" t="s">
         <v>42</v>
       </c>
@@ -28509,7 +28509,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A6" s="20" t="s">
         <v>48</v>
       </c>
@@ -28565,7 +28565,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A7" s="20" t="s">
         <v>534</v>
       </c>
@@ -28621,7 +28621,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A8" s="20" t="s">
         <v>824</v>
       </c>
@@ -28659,7 +28659,7 @@
       </c>
       <c r="R8" s="81"/>
     </row>
-    <row r="9" spans="1:18" ht="15.75" thickBot="1">
+    <row r="9" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A9" s="20" t="s">
         <v>1078</v>
       </c>
@@ -28685,7 +28685,7 @@
       <c r="Q9" s="81"/>
       <c r="R9" s="81"/>
     </row>
-    <row r="10" spans="1:18" ht="255.75" thickBot="1">
+    <row r="10" spans="1:18" ht="257" thickBot="1" x14ac:dyDescent="0.2">
       <c r="A10" s="20" t="s">
         <v>50</v>
       </c>
@@ -28741,7 +28741,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="15.75" thickBot="1">
+    <row r="11" spans="1:18" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A11" s="103" t="s">
         <v>63</v>
       </c>
@@ -28797,7 +28797,7 @@
         <v>3101</v>
       </c>
     </row>
-    <row r="12" spans="1:18">
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A12" s="136" t="s">
         <v>81</v>
       </c>
@@ -28853,7 +28853,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="7" customFormat="1">
+    <row r="13" spans="1:18" s="7" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A13" s="97"/>
       <c r="B13" s="134" t="s">
         <v>832</v>
@@ -28907,7 +28907,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="14" spans="1:18">
+    <row r="14" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A14" s="26"/>
       <c r="B14" s="27" t="s">
         <v>323</v>
@@ -28961,7 +28961,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="15" spans="1:18" ht="45">
+    <row r="15" spans="1:18" ht="48" x14ac:dyDescent="0.15">
       <c r="A15" s="21" t="s">
         <v>84</v>
       </c>
@@ -29017,7 +29017,7 @@
         <v>1098</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="105">
+    <row r="16" spans="1:18" ht="112" x14ac:dyDescent="0.15">
       <c r="A16"/>
       <c r="B16" s="19" t="s">
         <v>1099</v>
@@ -29071,7 +29071,7 @@
         <v>1104</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="135">
+    <row r="17" spans="1:18" ht="144" x14ac:dyDescent="0.15">
       <c r="A17" s="21"/>
       <c r="B17" s="19" t="s">
         <v>748</v>
@@ -29125,7 +29125,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="18" spans="1:18" ht="90">
+    <row r="18" spans="1:18" ht="96" x14ac:dyDescent="0.15">
       <c r="A18" s="21"/>
       <c r="B18" s="19" t="s">
         <v>1112</v>
@@ -29179,7 +29179,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="19" spans="1:18" ht="105">
+    <row r="19" spans="1:18" ht="112" x14ac:dyDescent="0.15">
       <c r="A19" s="21"/>
       <c r="B19" s="19" t="s">
         <v>1119</v>
@@ -29233,7 +29233,7 @@
         <v>1113</v>
       </c>
     </row>
-    <row r="20" spans="1:18" ht="105">
+    <row r="20" spans="1:18" ht="112" x14ac:dyDescent="0.15">
       <c r="A20" s="21"/>
       <c r="B20" s="19" t="s">
         <v>1128</v>
@@ -29285,7 +29285,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="60">
+    <row r="21" spans="1:18" ht="48" x14ac:dyDescent="0.15">
       <c r="B21" s="19" t="s">
         <v>1134</v>
       </c>
@@ -29316,7 +29316,7 @@
         <v>1135</v>
       </c>
     </row>
-    <row r="22" spans="1:18">
+    <row r="22" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A22" s="2"/>
       <c r="B22" s="2"/>
       <c r="C22" s="19"/>
@@ -29336,7 +29336,7 @@
       <c r="Q22" s="30"/>
       <c r="R22" s="30"/>
     </row>
-    <row r="23" spans="1:18">
+    <row r="23" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A23" s="13" t="s">
         <v>406</v>
       </c>
@@ -29392,7 +29392,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="24" spans="1:18">
+    <row r="24" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A24" s="2"/>
       <c r="B24" s="104" t="s">
         <v>132</v>
@@ -29446,7 +29446,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="25" spans="1:18">
+    <row r="25" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A25" s="2"/>
       <c r="B25" s="29" t="s">
         <v>133</v>
@@ -29500,7 +29500,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="26" spans="1:18">
+    <row r="26" spans="1:18" x14ac:dyDescent="0.15">
       <c r="A26" s="2"/>
       <c r="B26" s="31" t="s">
         <v>134</v>
@@ -29554,7 +29554,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="27" spans="1:18">
+    <row r="27" spans="1:18" x14ac:dyDescent="0.15">
       <c r="B27" s="46" t="s">
         <v>135</v>
       </c>
@@ -29607,7 +29607,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="28" spans="1:18">
+    <row r="28" spans="1:18" x14ac:dyDescent="0.15">
       <c r="B28" s="46" t="s">
         <v>409</v>
       </c>
@@ -29660,7 +29660,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="29" spans="1:18">
+    <row r="29" spans="1:18" x14ac:dyDescent="0.15">
       <c r="B29" s="46" t="s">
         <v>682</v>
       </c>
@@ -29713,7 +29713,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="30" spans="1:18">
+    <row r="30" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B30" s="46" t="s">
         <v>850</v>
       </c>
@@ -29766,7 +29766,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="31" spans="1:18">
+    <row r="31" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B31" s="46" t="s">
         <v>241</v>
       </c>
@@ -29819,7 +29819,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="32" spans="1:18">
+    <row r="32" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B32" s="69" t="s">
         <v>413</v>
       </c>
@@ -29872,7 +29872,7 @@
         <v>1139</v>
       </c>
     </row>
-    <row r="33" spans="2:18">
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B33" s="46" t="s">
         <v>852</v>
       </c>
@@ -29925,7 +29925,7 @@
         <v>859</v>
       </c>
     </row>
-    <row r="34" spans="2:18">
+    <row r="34" spans="2:18" x14ac:dyDescent="0.15">
       <c r="B34" s="46" t="s">
         <v>857</v>
       </c>
@@ -29978,7 +29978,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="35" spans="2:18">
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B35" s="46" t="s">
         <v>148</v>
       </c>
@@ -30023,7 +30023,7 @@
       </c>
       <c r="R35" s="31"/>
     </row>
-    <row r="36" spans="2:18">
+    <row r="36" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B36" s="46" t="s">
         <v>1138</v>
       </c>
@@ -30061,7 +30061,7 @@
       </c>
       <c r="R36" s="72"/>
     </row>
-    <row r="37" spans="2:18">
+    <row r="37" spans="2:18" x14ac:dyDescent="0.15">
       <c r="B37" s="46" t="s">
         <v>859</v>
       </c>
@@ -30093,7 +30093,7 @@
       </c>
       <c r="R37" s="72"/>
     </row>
-    <row r="38" spans="2:18">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.15">
       <c r="B38" s="46" t="s">
         <v>147</v>
       </c>
@@ -30120,7 +30120,7 @@
       <c r="Q38" s="33"/>
       <c r="R38" s="72"/>
     </row>
-    <row r="39" spans="2:18">
+    <row r="39" spans="2:18" x14ac:dyDescent="0.15">
       <c r="D39" s="31"/>
       <c r="H39" s="46" t="s">
         <v>147</v>
@@ -30145,7 +30145,7 @@
       </c>
       <c r="R39" s="72"/>
     </row>
-    <row r="40" spans="2:18">
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B40" s="107" t="s">
         <v>425</v>
       </c>
@@ -30186,7 +30186,7 @@
       <c r="Q40" s="33"/>
       <c r="R40" s="72"/>
     </row>
-    <row r="41" spans="2:18">
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B41" s="107" t="s">
         <v>426</v>
       </c>
@@ -30229,7 +30229,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="42" spans="2:18">
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B42" s="110" t="s">
         <v>146</v>
       </c>
@@ -30257,7 +30257,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="43" spans="2:18">
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B43" s="110" t="s">
         <v>149</v>
       </c>
@@ -30283,7 +30283,7 @@
       </c>
       <c r="Q43" s="33"/>
     </row>
-    <row r="44" spans="2:18">
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="H44" s="107" t="s">
         <v>426</v>
       </c>
@@ -30292,13 +30292,13 @@
       </c>
       <c r="P44" s="72"/>
     </row>
-    <row r="45" spans="2:18">
+    <row r="45" spans="2:18" x14ac:dyDescent="0.15">
       <c r="H45" s="110" t="s">
         <v>146</v>
       </c>
       <c r="P45" s="72"/>
     </row>
-    <row r="46" spans="2:18">
+    <row r="46" spans="2:18" x14ac:dyDescent="0.15">
       <c r="E46" s="19"/>
       <c r="F46" s="35" t="s">
         <v>860</v>
@@ -30307,67 +30307,67 @@
         <v>149</v>
       </c>
     </row>
-    <row r="47" spans="2:18">
+    <row r="47" spans="2:18" x14ac:dyDescent="0.15">
       <c r="E47" s="19"/>
     </row>
-    <row r="48" spans="2:18">
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="P48" s="69"/>
     </row>
-    <row r="49" spans="16:16">
+    <row r="49" spans="16:16" x14ac:dyDescent="0.15">
       <c r="P49" s="72"/>
     </row>
-    <row r="50" spans="16:16">
+    <row r="50" spans="16:16" x14ac:dyDescent="0.15">
       <c r="P50" s="72"/>
     </row>
-    <row r="51" spans="16:16">
+    <row r="51" spans="16:16" x14ac:dyDescent="0.15">
       <c r="P51" s="72"/>
     </row>
-    <row r="52" spans="16:16">
+    <row r="52" spans="16:16" x14ac:dyDescent="0.15">
       <c r="P52" s="72"/>
     </row>
-    <row r="53" spans="16:16">
+    <row r="53" spans="16:16" x14ac:dyDescent="0.15">
       <c r="P53" s="72"/>
     </row>
-    <row r="54" spans="16:16">
+    <row r="54" spans="16:16" x14ac:dyDescent="0.15">
       <c r="P54" s="72"/>
     </row>
-    <row r="55" spans="16:16">
+    <row r="55" spans="16:16" x14ac:dyDescent="0.15">
       <c r="P55" s="72"/>
     </row>
-    <row r="56" spans="16:16">
+    <row r="56" spans="16:16" x14ac:dyDescent="0.15">
       <c r="P56" s="72"/>
     </row>
-    <row r="57" spans="16:16">
+    <row r="57" spans="16:16" x14ac:dyDescent="0.15">
       <c r="P57" s="72"/>
     </row>
-    <row r="58" spans="16:16">
+    <row r="58" spans="16:16" x14ac:dyDescent="0.15">
       <c r="P58" s="72"/>
     </row>
-    <row r="59" spans="16:16">
+    <row r="59" spans="16:16" x14ac:dyDescent="0.15">
       <c r="P59" s="72"/>
     </row>
-    <row r="60" spans="16:16">
+    <row r="60" spans="16:16" x14ac:dyDescent="0.15">
       <c r="P60" s="72"/>
     </row>
-    <row r="61" spans="16:16">
+    <row r="61" spans="16:16" x14ac:dyDescent="0.15">
       <c r="P61" s="72"/>
     </row>
-    <row r="62" spans="16:16">
+    <row r="62" spans="16:16" x14ac:dyDescent="0.15">
       <c r="P62" s="72"/>
     </row>
-    <row r="63" spans="16:16">
+    <row r="63" spans="16:16" x14ac:dyDescent="0.15">
       <c r="P63" s="72"/>
     </row>
-    <row r="64" spans="16:16">
+    <row r="64" spans="16:16" x14ac:dyDescent="0.15">
       <c r="P64" s="72"/>
     </row>
-    <row r="68" spans="17:17">
+    <row r="68" spans="17:17" x14ac:dyDescent="0.15">
       <c r="Q68" s="33"/>
     </row>
-    <row r="69" spans="17:17">
+    <row r="69" spans="17:17" x14ac:dyDescent="0.15">
       <c r="Q69" s="33"/>
     </row>
-    <row r="70" spans="17:17">
+    <row r="70" spans="17:17" x14ac:dyDescent="0.15">
       <c r="Q70" s="33"/>
     </row>
   </sheetData>
@@ -30632,6 +30632,15 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <lcf76f155ced4ddcb4097134ff3c332f xmlns="a451f375-63eb-4e86-8d34-45bcb3463324">
@@ -30642,23 +30651,46 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{342E327F-6767-45ED-A1B8-1761D1984773}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{342E327F-6767-45ED-A1B8-1761D1984773}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="a451f375-63eb-4e86-8d34-45bcb3463324"/>
+    <ds:schemaRef ds:uri="a0097241-6f03-42ce-a713-bd87d5bb0233"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C33B3AEE-CE9E-41E0-A1F4-D34F26CC7549}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A86767D-2F9A-4E19-AE98-5CDD80A15B7E}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3A86767D-2F9A-4E19-AE98-5CDD80A15B7E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C33B3AEE-CE9E-41E0-A1F4-D34F26CC7549}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="a0097241-6f03-42ce-a713-bd87d5bb0233"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="a451f375-63eb-4e86-8d34-45bcb3463324"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>